--- a/Proyecto_Tabla_de_datos_con_coordenadas.xlsx
+++ b/Proyecto_Tabla_de_datos_con_coordenadas.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="GROK" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="PRUEBA" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="PRUEBA" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="GROK" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="DEEPSEEK" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="CHATGPT" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="CLAUDE" sheetId="5" r:id="rId9"/>
@@ -21,29 +21,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="260">
+  <si>
+    <t>PRUEBA</t>
+  </si>
   <si>
     <t>IA</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>Predicción</t>
   </si>
   <si>
+    <t>Fecha</t>
+  </si>
+  <si>
     <t>Dia/Mes</t>
   </si>
   <si>
+    <t>Hora</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lugar </t>
   </si>
   <si>
     <t>Magnitud</t>
   </si>
   <si>
+    <t>Lugar predicho</t>
+  </si>
+  <si>
     <t>¿Acertó?</t>
   </si>
   <si>
     <t>Latitud ref.</t>
   </si>
   <si>
+    <t>Margen M</t>
+  </si>
+  <si>
     <t>Longitud ref.</t>
   </si>
   <si>
@@ -53,30 +71,156 @@
     <t>Nota geográfica</t>
   </si>
   <si>
+    <t>DEEPSEEK</t>
+  </si>
+  <si>
+    <t>TEST001</t>
+  </si>
+  <si>
+    <t>21-24 de septiembre de 2026</t>
+  </si>
+  <si>
+    <t>Región de Antofagasta, entre Iquique y Mejillones</t>
+  </si>
+  <si>
+    <t>M4.0-5.5</t>
+  </si>
+  <si>
+    <t>Costa de Valparaíso</t>
+  </si>
+  <si>
+    <t>M3.7</t>
+  </si>
+  <si>
+    <t>Interplaca (subducción Nazca-Sudamericana)</t>
+  </si>
+  <si>
+    <t>Costa desértica del Norte Grande, entre Iquique y Antofagasta</t>
+  </si>
+  <si>
+    <t>±0.3</t>
+  </si>
+  <si>
+    <t>Zona costera</t>
+  </si>
+  <si>
+    <t>Centro aproximado frente a Valparaíso</t>
+  </si>
+  <si>
+    <t>TEST002</t>
+  </si>
+  <si>
+    <t>Región de Atacama, sector costero entre Copiapó y Vallenar</t>
+  </si>
+  <si>
+    <t>M4.0-5.0</t>
+  </si>
+  <si>
     <t>GROK</t>
   </si>
   <si>
-    <t>PRUEBA</t>
+    <t>Costa de Coquimbo</t>
+  </si>
+  <si>
+    <t>Interplaca con posible acoplamiento profundo</t>
+  </si>
+  <si>
+    <t>M4.1</t>
+  </si>
+  <si>
+    <t>Borde costero de Atacama, transición entre Norte Chico y Norte Grande</t>
+  </si>
+  <si>
+    <t>Centro aproximado frente a Coquimbo/La Serena</t>
+  </si>
+  <si>
+    <t>TEST003</t>
+  </si>
+  <si>
+    <t>Región de Coquimbo, cercanías de La Serena-Ovalle</t>
+  </si>
+  <si>
+    <t>M3.5-4.8</t>
+  </si>
+  <si>
+    <t>Costa de Antofagasta</t>
+  </si>
+  <si>
+    <t>M3.5</t>
+  </si>
+  <si>
+    <t>±0.2</t>
+  </si>
+  <si>
+    <t>Interplaca / transición</t>
+  </si>
+  <si>
+    <t>Valle del Elqui y borde costero de Coquimbo</t>
+  </si>
+  <si>
+    <t>Centro aproximado frente a Antofagasta</t>
+  </si>
+  <si>
+    <t>TEST004</t>
+  </si>
+  <si>
+    <t>Región Metropolitana, sector Farellones-Cajón del Maipo</t>
+  </si>
+  <si>
+    <t>M3.0-4.5</t>
+  </si>
+  <si>
+    <t>Costa de Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">11-13 de septiembre </t>
   </si>
   <si>
-    <t>ID</t>
+    <t>M4.4</t>
+  </si>
+  <si>
+    <t>Intraplaca (deformación interna de Nazca)</t>
+  </si>
+  <si>
+    <t>±0.4</t>
+  </si>
+  <si>
+    <t>Precordillera andina, al este de Santiago</t>
+  </si>
+  <si>
+    <t>Centro aproximado frente a Tarapacá</t>
+  </si>
+  <si>
+    <t>Región del Biobío, zona de Concepción-Arauco</t>
+  </si>
+  <si>
+    <t>TEST005</t>
+  </si>
+  <si>
+    <t>Región de Atacama</t>
+  </si>
+  <si>
+    <t>Interplaca (subducción)</t>
+  </si>
+  <si>
+    <t>M3.9</t>
+  </si>
+  <si>
+    <t>Golfo de Arauco y península de Tumbes, zona de gran acoplamiento histórico</t>
+  </si>
+  <si>
+    <t>Región amplia</t>
+  </si>
+  <si>
+    <t>Referencia aproximada: zona de Copiapó</t>
   </si>
   <si>
     <t xml:space="preserve">Franja Tarapacá–Antofagasta </t>
   </si>
   <si>
-    <t>Fecha</t>
-  </si>
-  <si>
     <t>3.0–4.5</t>
   </si>
   <si>
-    <t>Hora</t>
-  </si>
-  <si>
     <t>Franja amplia</t>
   </si>
   <si>
@@ -89,18 +233,12 @@
     <t>Zona de Calama / Ollagüe (Antofagasta – Tarapacá).</t>
   </si>
   <si>
-    <t>Lugar predicho</t>
-  </si>
-  <si>
     <t>3.2 – 4.3</t>
   </si>
   <si>
     <t>Zona interior</t>
   </si>
   <si>
-    <t>Margen M</t>
-  </si>
-  <si>
     <t>Centro aproximado Calama–Ollagüe</t>
   </si>
   <si>
@@ -113,9 +251,6 @@
     <t>2.8 – 4.0</t>
   </si>
   <si>
-    <t>DEEPSEEK</t>
-  </si>
-  <si>
     <t>Centro aproximado Pica–Collahuasi–La Tirana</t>
   </si>
   <si>
@@ -140,9 +275,6 @@
     <t>Zona de Coquimbo / Ovalle o La Serena</t>
   </si>
   <si>
-    <t>TEST001</t>
-  </si>
-  <si>
     <t>2.7 – 3.8</t>
   </si>
   <si>
@@ -152,91 +284,409 @@
     <t>Centro aproximado La Serena–Coquimbo–Ovalle</t>
   </si>
   <si>
-    <t>Costa de Valparaíso</t>
-  </si>
-  <si>
-    <t>M3.7</t>
-  </si>
-  <si>
-    <t>±0.3</t>
-  </si>
-  <si>
-    <t>Zona costera</t>
-  </si>
-  <si>
-    <t>Centro aproximado frente a Valparaíso</t>
-  </si>
-  <si>
-    <t>TEST002</t>
-  </si>
-  <si>
-    <t>Costa de Coquimbo</t>
-  </si>
-  <si>
-    <t>M4.1</t>
-  </si>
-  <si>
-    <t>Centro aproximado frente a Coquimbo/La Serena</t>
-  </si>
-  <si>
-    <t>TEST003</t>
-  </si>
-  <si>
-    <t>Costa de Antofagasta</t>
-  </si>
-  <si>
-    <t>M3.5</t>
-  </si>
-  <si>
-    <t>±0.2</t>
-  </si>
-  <si>
-    <t>Centro aproximado frente a Antofagasta</t>
-  </si>
-  <si>
-    <t>TEST004</t>
-  </si>
-  <si>
-    <t>Costa de Tarapacá</t>
-  </si>
-  <si>
-    <t>M4.4</t>
-  </si>
-  <si>
-    <t>±0.4</t>
-  </si>
-  <si>
-    <t>Centro aproximado frente a Tarapacá</t>
-  </si>
-  <si>
-    <t>TEST005</t>
-  </si>
-  <si>
-    <t>Región de Atacama</t>
-  </si>
-  <si>
-    <t>M3.9</t>
-  </si>
-  <si>
-    <t>Región amplia</t>
-  </si>
-  <si>
-    <t>Referencia aproximada: zona de Copiapó</t>
+    <t>CLAUDE</t>
+  </si>
+  <si>
+    <t>11-13 sept, 00:00-06:00</t>
+  </si>
+  <si>
+    <t>Costa Iquique-Tocopilla</t>
+  </si>
+  <si>
+    <t>Franja costera</t>
+  </si>
+  <si>
+    <t>Centro aproximado Iquique–Tocopilla</t>
+  </si>
+  <si>
+    <t>11-13 sept, 12:00-18:00</t>
+  </si>
+  <si>
+    <t>Costa Valparaíso-San Antonio</t>
+  </si>
+  <si>
+    <t>M3.2</t>
+  </si>
+  <si>
+    <t>Centro aproximado Valparaíso–San Antonio</t>
+  </si>
+  <si>
+    <t>11-13 sept, 06:00-12:00</t>
+  </si>
+  <si>
+    <t>Costa Maule-Biobío</t>
+  </si>
+  <si>
+    <t>M3.8</t>
+  </si>
+  <si>
+    <t>Franja costera amplia</t>
+  </si>
+  <si>
+    <t>Centro aproximado costa Maule–Biobío</t>
+  </si>
+  <si>
+    <t>11-13 sept, 18:00-00:00</t>
+  </si>
+  <si>
+    <t>Costa Antofagasta-Mejillones</t>
+  </si>
+  <si>
+    <t>M4.0</t>
+  </si>
+  <si>
+    <t>Centro aproximado Antofagasta–Mejillones</t>
+  </si>
+  <si>
+    <t>Costa Araucanía-Los Ríos</t>
+  </si>
+  <si>
+    <t>M3.4</t>
+  </si>
+  <si>
+    <t>Centro aproximado costa Araucanía–Los Ríos</t>
+  </si>
+  <si>
+    <t>PERPLEXITY</t>
+  </si>
+  <si>
+    <t>22/09/2026, 11:00-14:00</t>
+  </si>
+  <si>
+    <t>20-30 km al NO de La Serena, Coquimbo</t>
+  </si>
+  <si>
+    <t>M4.0-4.5</t>
+  </si>
+  <si>
+    <t>Subducción interplaca</t>
+  </si>
+  <si>
+    <t>META AI</t>
+  </si>
+  <si>
+    <t>Zona de falla activa; 4 sismos M4.0+ en septiembre de 2026</t>
+  </si>
+  <si>
+    <t>22/09/2026, 18:00-22:00</t>
+  </si>
+  <si>
+    <t>15-25 km al SE de Valparaíso, Valparaíso</t>
+  </si>
+  <si>
+    <t>M3.5-4.0</t>
+  </si>
+  <si>
+    <t>Cercano a falla de San Ramón; zona central sísmicamente activa</t>
+  </si>
+  <si>
+    <t>22/09 18:00 a 24/09 08:00</t>
+  </si>
+  <si>
+    <t>23/09/2026, 09:00-13:00</t>
+  </si>
+  <si>
+    <t>30-40 km al O de Pichilemu, O'Higgins</t>
+  </si>
+  <si>
+    <t>Antofagasta interior-San Pedro / Calama</t>
+  </si>
+  <si>
+    <t>M3.8-4.3</t>
+  </si>
+  <si>
+    <t>M3.8-4.5</t>
+  </si>
+  <si>
+    <t>Zona de ruptura del terremoto M8.8 de 2010; estrés tectónico residual</t>
+  </si>
+  <si>
+    <t>Intraplaca intermedia</t>
+  </si>
+  <si>
+    <t>Placa de Nazca subductada a 100-130 km; eventos recientes en Mina Escondida y Ollagüe</t>
+  </si>
+  <si>
+    <t>23/09/2026, 20:00-23:00</t>
+  </si>
+  <si>
+    <t>25-35 km al NE de Antofagasta, Antofagasta</t>
+  </si>
+  <si>
+    <t>M3.3-3.8</t>
+  </si>
+  <si>
+    <t>23/09 10:00 a 24/09 23:00</t>
+  </si>
+  <si>
+    <t>Atacama costa-SO de Copiapó / Caldera offshore</t>
+  </si>
+  <si>
+    <t>Norte Grande; actividad sísmica constante por subducción de la placa de Nazca</t>
+  </si>
+  <si>
+    <t>M3.2-4.0</t>
+  </si>
+  <si>
+    <t>24/09/2026, 06:00-10:00</t>
+  </si>
+  <si>
+    <t>Interplaca somera-contacto</t>
+  </si>
+  <si>
+    <t>10-20 km al S de Puerto Montt, Los Lagos</t>
+  </si>
+  <si>
+    <t>Frente a la fosa; laguna sísmica de Atacama y acumulación de energía somera</t>
+  </si>
+  <si>
+    <t>M3.6-4.1</t>
+  </si>
+  <si>
+    <t>22/09 20:00 a 23/09 22:00</t>
+  </si>
+  <si>
+    <t>Coquimbo-O de La Serena offshore</t>
+  </si>
+  <si>
+    <t>Zona sur; cercana a falla de Liquiñe-Ofqui; actividad volcánica asociada</t>
+  </si>
+  <si>
+    <t>M3.0-4.2</t>
+  </si>
+  <si>
+    <t>Norte Chico; segundo peak nacional de sismicidad y actividad constante</t>
+  </si>
+  <si>
+    <t>23/09 00:00 a 25/09 06:00</t>
+  </si>
+  <si>
+    <t>Tarapacá interior-E de Iquique / Pica</t>
+  </si>
+  <si>
+    <t>M3.5-4.3</t>
+  </si>
+  <si>
+    <t>Subducción profunda bajo la Pampa del Tamarugal; sismos de 90-115 km frecuentes</t>
+  </si>
+  <si>
+    <t>22/09 22:00 a 24/09 18:00</t>
+  </si>
+  <si>
+    <t>Zona Central-O de Valparaíso / San Antonio offshore</t>
+  </si>
+  <si>
+    <t>M2.8-3.8</t>
+  </si>
+  <si>
+    <t>Segmento Los Vilos-Pichilemu; energía acumulada hacia la trinchera</t>
   </si>
   <si>
     <t>CHATGPT</t>
   </si>
   <si>
+    <t>MISTRAL AI</t>
+  </si>
+  <si>
+    <t>21/09/2026 07:08</t>
+  </si>
+  <si>
+    <t>35 km al S de Mina Collahuasi</t>
+  </si>
+  <si>
+    <t>M3.0</t>
+  </si>
+  <si>
+    <t>Zona andina (intraplaca)</t>
+  </si>
+  <si>
+    <t>Altiplano, cerca de la frontera con Bolivia; profundidad probable de 121 km</t>
+  </si>
+  <si>
+    <t>21/09/2026 06:50</t>
+  </si>
+  <si>
+    <t>84 km al SE de Socaire</t>
+  </si>
+  <si>
+    <t>GEMINI</t>
+  </si>
+  <si>
+    <t>Zona de fallas intraplaca</t>
+  </si>
+  <si>
+    <t>Altiplano andino; deformación interna de la placa; profundidad probable de 235 km</t>
+  </si>
+  <si>
+    <t>21/09/2026 06:36</t>
+  </si>
+  <si>
+    <t>48 km al E de Socaire</t>
+  </si>
+  <si>
+    <t>22/09/2026 09:15 UTC (24 h)</t>
+  </si>
+  <si>
+    <t>Tarapacá, interior de Pica</t>
+  </si>
+  <si>
+    <t>Zona andina</t>
+  </si>
+  <si>
+    <t>Mw 3.8-4.3</t>
+  </si>
+  <si>
+    <t>Altiplano, cerca de la Cordillera de los Andes; profundidad probable de 261 km</t>
+  </si>
+  <si>
+    <t>21/09/2026 06:03</t>
+  </si>
+  <si>
+    <t>Intraplaca intermedia-profunda</t>
+  </si>
+  <si>
+    <t>3 km al SO de Mejillones</t>
+  </si>
+  <si>
+    <t>Alta recurrencia de sismicidad intraplaca intermedia a profunda</t>
+  </si>
+  <si>
+    <t>M2.8</t>
+  </si>
+  <si>
+    <t>Zona de subducción</t>
+  </si>
+  <si>
+    <t>22/09/2026 21:40 UTC (24 h)</t>
+  </si>
+  <si>
+    <t>Costa de Antofagasta, sobre la fosa Perú-Chile; profundidad probable de 54 km</t>
+  </si>
+  <si>
+    <t>Antofagasta, Socaire / Cordillera</t>
+  </si>
+  <si>
+    <t>Mw 4.0-4.6</t>
+  </si>
+  <si>
+    <t>21/09/2026 04:19</t>
+  </si>
+  <si>
+    <t>Plano de subducción profundo</t>
+  </si>
+  <si>
+    <t>20 km al NO de Mejillones</t>
+  </si>
+  <si>
+    <t>Frecuente liberación de energía en el plano de subducción a más de 100 km</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:10 UTC (48 h)</t>
+  </si>
+  <si>
+    <t>Costa de Valparaíso offshore</t>
+  </si>
+  <si>
+    <t>Mw 3.2-3.7</t>
+  </si>
+  <si>
+    <t>Interplaca somera</t>
+  </si>
+  <si>
+    <t>Sismicidad interplaca menor continua debido al acoplamiento de placas</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:25 UTC (48 h)</t>
+  </si>
+  <si>
+    <t>Atacama, costa de Caldera</t>
+  </si>
+  <si>
+    <t>Mw 3.5-4.1</t>
+  </si>
+  <si>
+    <t>Interplaca costera</t>
+  </si>
+  <si>
+    <t>Liberaciones menores habituales en el segmento costero</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:05 UTC (72 h)</t>
+  </si>
+  <si>
+    <t>Biobío, península de Arauco</t>
+  </si>
+  <si>
+    <t>Mw 3.0-3.6</t>
+  </si>
+  <si>
+    <t>Interplaca / placa superior</t>
+  </si>
+  <si>
+    <t>Reajuste cortical postsísmico y deformación continua de la placa superior</t>
+  </si>
+  <si>
     <t>10 - 13/09/2026</t>
   </si>
   <si>
+    <t>Costa de Antofagasta; alta actividad sísmica por subducción; profundidad probable de 25 km</t>
+  </si>
+  <si>
+    <t>COPILOT</t>
+  </si>
+  <si>
+    <t>10-13 de septiembre</t>
+  </si>
+  <si>
+    <t>Región de Coquimbo y Antofagasta</t>
+  </si>
+  <si>
+    <t>4.0/5.5</t>
+  </si>
+  <si>
+    <t>Macro-zona</t>
+  </si>
+  <si>
+    <t>Centro aproximado entre ambas regiones</t>
+  </si>
+  <si>
+    <t>Región del Biobío o La Araucanía</t>
+  </si>
+  <si>
+    <t>3.8/4.8</t>
+  </si>
+  <si>
     <t>Costa de Tarapacá - Antofagasta</t>
   </si>
   <si>
+    <t>Centro aproximado Biobío–Araucanía</t>
+  </si>
+  <si>
+    <t>Región de Aysén</t>
+  </si>
+  <si>
+    <t>3.5/4.5</t>
+  </si>
+  <si>
+    <t>Referencia aproximada: Coyhaique</t>
+  </si>
+  <si>
     <t>M4,0 - 5,0</t>
   </si>
   <si>
-    <t>Franja costera amplia</t>
+    <t>Región de Valparaíso o Metropolitana (Santiago)</t>
+  </si>
+  <si>
+    <t>4.2/5.0</t>
+  </si>
+  <si>
+    <t>Centro aproximado Valparaíso–Santiago</t>
+  </si>
+  <si>
+    <t>Región de Arica y Parinacota o Tarapacá</t>
+  </si>
+  <si>
+    <t>Centro aproximado Arica–Tarapacá</t>
   </si>
   <si>
     <t>Centro aproximado costa Tarapacá–Antofagasta</t>
@@ -278,133 +728,79 @@
     <t>M3,5–5,0</t>
   </si>
   <si>
-    <t>Macro-zona</t>
-  </si>
-  <si>
     <t>Centro aproximado Antofagasta–Coquimbo</t>
   </si>
   <si>
-    <t>CLAUDE</t>
-  </si>
-  <si>
-    <t>11-13 sept, 00:00-06:00</t>
-  </si>
-  <si>
-    <t>Costa Iquique-Tocopilla</t>
-  </si>
-  <si>
-    <t>Franja costera</t>
-  </si>
-  <si>
-    <t>Centro aproximado Iquique–Tocopilla</t>
-  </si>
-  <si>
-    <t>11-13 sept, 12:00-18:00</t>
-  </si>
-  <si>
-    <t>Costa Valparaíso-San Antonio</t>
-  </si>
-  <si>
-    <t>M3.2</t>
-  </si>
-  <si>
-    <t>Centro aproximado Valparaíso–San Antonio</t>
-  </si>
-  <si>
-    <t>11-13 sept, 06:00-12:00</t>
-  </si>
-  <si>
-    <t>Costa Maule-Biobío</t>
-  </si>
-  <si>
-    <t>M3.8</t>
-  </si>
-  <si>
-    <t>Centro aproximado costa Maule–Biobío</t>
-  </si>
-  <si>
-    <t>11-13 sept, 18:00-00:00</t>
-  </si>
-  <si>
-    <t>Costa Antofagasta-Mejillones</t>
-  </si>
-  <si>
-    <t>M4.0</t>
-  </si>
-  <si>
-    <t>Centro aproximado Antofagasta–Mejillones</t>
-  </si>
-  <si>
-    <t>Costa Araucanía-Los Ríos</t>
-  </si>
-  <si>
-    <t>M3.4</t>
-  </si>
-  <si>
-    <t>Centro aproximado costa Araucanía–Los Ríos</t>
-  </si>
-  <si>
-    <t>PERPLEXITY</t>
-  </si>
-  <si>
-    <t>META AI</t>
-  </si>
-  <si>
-    <t>MISTRAL AI</t>
-  </si>
-  <si>
-    <t>GEMINI</t>
-  </si>
-  <si>
-    <t>COPILOT</t>
-  </si>
-  <si>
-    <t>10-13 de septiembre</t>
-  </si>
-  <si>
-    <t>Región de Coquimbo y Antofagasta</t>
-  </si>
-  <si>
-    <t>4.0/5.5</t>
-  </si>
-  <si>
-    <t>Centro aproximado entre ambas regiones</t>
-  </si>
-  <si>
-    <t>Región del Biobío o La Araucanía</t>
-  </si>
-  <si>
-    <t>3.8/4.8</t>
-  </si>
-  <si>
-    <t>Centro aproximado Biobío–Araucanía</t>
-  </si>
-  <si>
-    <t>Región de Aysén</t>
-  </si>
-  <si>
-    <t>3.5/4.5</t>
-  </si>
-  <si>
-    <t>Referencia aproximada: Coyhaique</t>
-  </si>
-  <si>
-    <t>Región de Valparaíso o Metropolitana (Santiago)</t>
-  </si>
-  <si>
-    <t>4.2/5.0</t>
-  </si>
-  <si>
-    <t>Centro aproximado Valparaíso–Santiago</t>
-  </si>
-  <si>
-    <t>Región de Arica y Parinacota o Tarapacá</t>
-  </si>
-  <si>
-    <t>Centro aproximado Arica–Tarapacá</t>
-  </si>
-  <si>
     <t>QWEN</t>
+  </si>
+  <si>
+    <t>23-24/09/2026, diurno o vespertino</t>
+  </si>
+  <si>
+    <t>Norte Grande: Ollagüe / Mina Collahuasi</t>
+  </si>
+  <si>
+    <t>M3.5-4.5</t>
+  </si>
+  <si>
+    <t>Subducción intermedia / intraplaca</t>
+  </si>
+  <si>
+    <t>Placa de Nazca bajo el altiplano a unos 100-120 km de profundidad</t>
+  </si>
+  <si>
+    <t>24/09/2026, cualquier hora</t>
+  </si>
+  <si>
+    <t>Mejillones / península de Mejillones</t>
+  </si>
+  <si>
+    <t>Interplaca superficial / falla cortical costera</t>
+  </si>
+  <si>
+    <t>Zona de acoplamiento sísmico y fallas locales en la corteza oceánica y costera</t>
+  </si>
+  <si>
+    <t>23-25/09/2026, horario nocturno</t>
+  </si>
+  <si>
+    <t>Zona Central: Rancagua / Cachapoal</t>
+  </si>
+  <si>
+    <t>M2.5-3.5</t>
+  </si>
+  <si>
+    <t>Intraplaca / falla cortical</t>
+  </si>
+  <si>
+    <t>Actividad en la placa continental, alejada de la interfaz principal de subducción</t>
+  </si>
+  <si>
+    <t>24-25/09/2026, horario matutino</t>
+  </si>
+  <si>
+    <t>Zona Sur: Valdivia / Lago Ranco</t>
+  </si>
+  <si>
+    <t>M3.0-4.0</t>
+  </si>
+  <si>
+    <t>Falla Liquiñe-Ofqui / subducción</t>
+  </si>
+  <si>
+    <t>Zona de transición tectónica compleja con presencia de fluidos hidrotermales</t>
+  </si>
+  <si>
+    <t>23-25/09/2026, cualquier hora</t>
+  </si>
+  <si>
+    <t>Zona Austral: península de Taitao / golfo de Penas</t>
+  </si>
+  <si>
+    <t>Triple unión / fallas locales</t>
+  </si>
+  <si>
+    <t>Triple unión de las placas de Nazca, Antártica y Sudamericana</t>
   </si>
 </sst>
 </file>
@@ -414,7 +810,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -427,24 +823,19 @@
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font/>
     <font>
@@ -453,12 +844,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -513,6 +904,11 @@
       </right>
     </border>
     <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -523,64 +919,69 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
@@ -588,11 +989,6 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -850,13 +1246,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="12.63"/>
-    <col customWidth="1" min="4" max="4" width="16.63"/>
-    <col customWidth="1" min="5" max="5" width="45.5"/>
-    <col customWidth="1" min="6" max="6" width="19.13"/>
-    <col customWidth="1" min="8" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="1" max="5" width="12.63"/>
+    <col customWidth="1" min="6" max="6" width="18.5"/>
+    <col customWidth="1" min="9" max="10" width="13.0"/>
+    <col customWidth="1" min="11" max="11" width="20.0"/>
+    <col customWidth="1" min="12" max="12" width="38.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
@@ -864,234 +1258,218 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="10">
-        <v>-21.9</v>
-      </c>
-      <c r="I3" s="10">
-        <v>-69.8</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>19</v>
+      <c r="B3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8">
+        <v>46275.0</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0.5625</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="13">
+        <v>-33.05</v>
+      </c>
+      <c r="J3" s="13">
+        <v>-71.85</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="10">
-        <v>-21.95</v>
-      </c>
-      <c r="I4" s="10">
-        <v>-68.75</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="10" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="8">
+        <v>46275.0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.5868055555555556</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="13">
+        <v>-29.95</v>
+      </c>
+      <c r="J4" s="13">
+        <v>-71.55</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>26</v>
       </c>
+      <c r="L4" s="13" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="10">
-        <v>-20.55</v>
-      </c>
-      <c r="I5" s="10">
-        <v>-69.25</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>31</v>
+      <c r="B5" s="14"/>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="8">
+        <v>46275.0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="13">
+        <v>-23.65</v>
+      </c>
+      <c r="J5" s="13">
+        <v>-70.65</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="10">
-        <v>-27.35</v>
-      </c>
-      <c r="I6" s="10">
-        <v>-69.7</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>36</v>
+      <c r="B6" s="14"/>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="8">
+        <v>46275.0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="13">
+        <v>-20.2</v>
+      </c>
+      <c r="J6" s="13">
+        <v>-70.4</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="10">
-        <v>-30.2</v>
-      </c>
-      <c r="I7" s="10">
-        <v>-71.15</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>42</v>
+      <c r="B7" s="14"/>
+      <c r="C7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="8">
+        <v>46275.0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0.6631944444444444</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="13">
+        <v>-27.37</v>
+      </c>
+      <c r="J7" s="13">
+        <v>-70.33</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="B8" s="17"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="B9" s="19"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="B10" s="19"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-    </row>
+      <c r="B11" s="19"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1"/>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2081,7 +2459,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:B12"/>
+    <mergeCell ref="B3:B7"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -2108,228 +2486,228 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="10">
+      <c r="D3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="13">
         <v>-26.8</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="13">
         <v>-70.5</v>
       </c>
-      <c r="J3" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>115</v>
+      <c r="J3" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="10">
+      <c r="D4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="13">
         <v>-37.8</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="13">
         <v>-72.6</v>
       </c>
-      <c r="J4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>118</v>
+      <c r="J4" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="10">
+      <c r="D5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="13">
         <v>-45.57</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="13">
         <v>-72.07</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>121</v>
+      <c r="J5" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="10">
+      <c r="D6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="13">
         <v>-33.3</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="13">
         <v>-71.0</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>124</v>
+      <c r="J6" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="10">
+      <c r="D7" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="13">
         <v>-19.4</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="13">
         <v>-69.8</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>126</v>
+      <c r="J7" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -3337,147 +3715,240 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="5" width="12.63"/>
-    <col customWidth="1" min="6" max="6" width="7.88"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="42.0"/>
+    <col customWidth="1" min="6" max="6" width="14.0"/>
+    <col customWidth="1" min="7" max="7" width="12.0"/>
     <col customWidth="1" min="8" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="11" width="58.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="1">
+      <c r="B3" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="D3" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11">
+        <v>-21.5</v>
+      </c>
+      <c r="I3" s="11">
+        <v>-68.5</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" ht="24.0" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="D4" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11">
+        <v>-23.0</v>
+      </c>
+      <c r="I4" s="11">
+        <v>-70.8</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" ht="24.0" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="D5" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11">
+        <v>-34.2</v>
+      </c>
+      <c r="I5" s="11">
+        <v>-70.7</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" ht="15.0" customHeight="1">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="D6" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="11">
+        <v>-40.0</v>
+      </c>
+      <c r="I6" s="11">
+        <v>-72.5</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" ht="15.0" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="D7" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="11">
+        <v>-46.5</v>
+      </c>
+      <c r="I7" s="11">
+        <v>-74.5</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -4485,230 +4956,248 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="5" width="12.63"/>
-    <col customWidth="1" min="6" max="6" width="18.5"/>
-    <col customWidth="1" min="9" max="10" width="13.0"/>
-    <col customWidth="1" min="11" max="11" width="20.0"/>
-    <col customWidth="1" min="12" max="12" width="38.0"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="16.63"/>
+    <col customWidth="1" min="5" max="5" width="45.5"/>
+    <col customWidth="1" min="6" max="6" width="19.13"/>
+    <col customWidth="1" min="8" max="9" width="13.0"/>
+    <col customWidth="1" min="10" max="10" width="20.0"/>
+    <col customWidth="1" min="11" max="11" width="38.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="13">
-        <v>46275.0</v>
-      </c>
-      <c r="E3" s="14">
-        <v>0.5625</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="10">
-        <v>-33.05</v>
-      </c>
-      <c r="J3" s="10">
-        <v>-71.85</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>47</v>
+      <c r="B3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="13">
+        <v>-21.9</v>
+      </c>
+      <c r="I3" s="13">
+        <v>-69.8</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="13">
-        <v>46275.0</v>
-      </c>
-      <c r="E4" s="14">
-        <v>0.5868055555555556</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="10">
-        <v>-29.95</v>
-      </c>
-      <c r="J4" s="10">
-        <v>-71.55</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>51</v>
+      <c r="B4" s="14"/>
+      <c r="C4" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="13">
+        <v>-21.95</v>
+      </c>
+      <c r="I4" s="13">
+        <v>-68.75</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="13">
-        <v>46275.0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="10">
-        <v>-23.65</v>
-      </c>
-      <c r="J5" s="10">
-        <v>-70.65</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>56</v>
+      <c r="B5" s="14"/>
+      <c r="C5" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="13">
+        <v>-20.55</v>
+      </c>
+      <c r="I5" s="13">
+        <v>-69.25</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="13">
-        <v>46275.0</v>
-      </c>
-      <c r="E6" s="14">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="10">
-        <v>-20.2</v>
-      </c>
-      <c r="J6" s="10">
-        <v>-70.4</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>61</v>
+      <c r="B6" s="14"/>
+      <c r="C6" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="13">
+        <v>-27.35</v>
+      </c>
+      <c r="I6" s="13">
+        <v>-69.7</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="13">
-        <v>46275.0</v>
-      </c>
-      <c r="E7" s="14">
-        <v>0.6631944444444444</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="10">
-        <v>-27.37</v>
-      </c>
-      <c r="J7" s="10">
-        <v>-70.33</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>66</v>
+      <c r="B7" s="14"/>
+      <c r="C7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="13">
+        <v>-30.2</v>
+      </c>
+      <c r="I7" s="13">
+        <v>-71.15</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="19"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="17"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="17"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="17"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="B12" s="20"/>
+      <c r="C12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+    </row>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1"/>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -5698,7 +6187,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B3:B12"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -5714,147 +6203,240 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
-    <col customWidth="1" min="5" max="6" width="12.88"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="42.0"/>
+    <col customWidth="1" min="6" max="6" width="14.0"/>
+    <col customWidth="1" min="7" max="7" width="12.0"/>
     <col customWidth="1" min="8" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="11" width="58.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="24.0" customHeight="1">
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11">
+        <v>-23.5</v>
+      </c>
+      <c r="I3" s="11">
+        <v>-70.5</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="24.0" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="G4" s="9"/>
+      <c r="H4" s="11">
+        <v>-28.0</v>
+      </c>
+      <c r="I4" s="11">
+        <v>-70.8</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="15.0" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11">
+        <v>-30.0</v>
+      </c>
+      <c r="I5" s="11">
+        <v>-71.2</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="24.0" customHeight="1">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="D6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="11">
+        <v>-33.4</v>
+      </c>
+      <c r="I6" s="11">
+        <v>-70.3</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" ht="24.0" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="D7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="11">
+        <v>-36.8</v>
+      </c>
+      <c r="I7" s="11">
+        <v>-73.0</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -6872,855 +7454,855 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="D1" s="18"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="10">
+      <c r="D3" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="13">
         <v>-21.9</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="13">
         <v>-70.35</v>
       </c>
-      <c r="J3" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>72</v>
+      <c r="J3" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="10">
+      <c r="D4" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="13">
         <v>-28.9</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="13">
         <v>-71.45</v>
       </c>
-      <c r="J4" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>75</v>
+      <c r="J4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="10">
+      <c r="D5" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="13">
         <v>-33.8</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="13">
         <v>-71.2</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>79</v>
+      <c r="J5" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="10">
+      <c r="D6" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="13">
         <v>-37.0</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="13">
         <v>-72.2</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>82</v>
+      <c r="J6" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="10">
+      <c r="D7" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="13">
         <v>-27.0</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="13">
         <v>-70.6</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>86</v>
+      <c r="J7" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="D13" s="18"/>
+      <c r="D13" s="22"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="D14" s="18"/>
+      <c r="D14" s="22"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="D15" s="18"/>
+      <c r="D15" s="22"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="D16" s="18"/>
+      <c r="D16" s="22"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="D17" s="18"/>
+      <c r="D17" s="22"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="D18" s="18"/>
+      <c r="D18" s="22"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="D19" s="18"/>
+      <c r="D19" s="22"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="D20" s="18"/>
+      <c r="D20" s="22"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="D21" s="18"/>
+      <c r="D21" s="22"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="D22" s="18"/>
+      <c r="D22" s="22"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="D23" s="18"/>
+      <c r="D23" s="22"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="D24" s="18"/>
+      <c r="D24" s="22"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="D25" s="18"/>
+      <c r="D25" s="22"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="D26" s="18"/>
+      <c r="D26" s="22"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="D27" s="18"/>
+      <c r="D27" s="22"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="D28" s="18"/>
+      <c r="D28" s="22"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="D29" s="18"/>
+      <c r="D29" s="22"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="D30" s="18"/>
+      <c r="D30" s="22"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="D31" s="18"/>
+      <c r="D31" s="22"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="D32" s="18"/>
+      <c r="D32" s="22"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="D33" s="18"/>
+      <c r="D33" s="22"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="D34" s="18"/>
+      <c r="D34" s="22"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="D35" s="18"/>
+      <c r="D35" s="22"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="D36" s="18"/>
+      <c r="D36" s="22"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="D37" s="18"/>
+      <c r="D37" s="22"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="D38" s="18"/>
+      <c r="D38" s="22"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="D39" s="18"/>
+      <c r="D39" s="22"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="D40" s="18"/>
+      <c r="D40" s="22"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="D41" s="18"/>
+      <c r="D41" s="22"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="D42" s="18"/>
+      <c r="D42" s="22"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="D43" s="18"/>
+      <c r="D43" s="22"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="D44" s="18"/>
+      <c r="D44" s="22"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="D45" s="18"/>
+      <c r="D45" s="22"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="D46" s="18"/>
+      <c r="D46" s="22"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="D47" s="18"/>
+      <c r="D47" s="22"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="D48" s="18"/>
+      <c r="D48" s="22"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="D49" s="18"/>
+      <c r="D49" s="22"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="D50" s="18"/>
+      <c r="D50" s="22"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="D51" s="18"/>
+      <c r="D51" s="22"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="D52" s="18"/>
+      <c r="D52" s="22"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="D53" s="18"/>
+      <c r="D53" s="22"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="D54" s="18"/>
+      <c r="D54" s="22"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="D55" s="18"/>
+      <c r="D55" s="22"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="D56" s="18"/>
+      <c r="D56" s="22"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="D57" s="18"/>
+      <c r="D57" s="22"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="D58" s="18"/>
+      <c r="D58" s="22"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="D59" s="18"/>
+      <c r="D59" s="22"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="D60" s="18"/>
+      <c r="D60" s="22"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="D61" s="18"/>
+      <c r="D61" s="22"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="D62" s="18"/>
+      <c r="D62" s="22"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="D63" s="18"/>
+      <c r="D63" s="22"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="D64" s="18"/>
+      <c r="D64" s="22"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="D65" s="18"/>
+      <c r="D65" s="22"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="D66" s="18"/>
+      <c r="D66" s="22"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="D67" s="18"/>
+      <c r="D67" s="22"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="D68" s="18"/>
+      <c r="D68" s="22"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="D69" s="18"/>
+      <c r="D69" s="22"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="D70" s="18"/>
+      <c r="D70" s="22"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="D71" s="18"/>
+      <c r="D71" s="22"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="D72" s="18"/>
+      <c r="D72" s="22"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="D73" s="18"/>
+      <c r="D73" s="22"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="D74" s="18"/>
+      <c r="D74" s="22"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="D75" s="18"/>
+      <c r="D75" s="22"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="D76" s="18"/>
+      <c r="D76" s="22"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="D77" s="18"/>
+      <c r="D77" s="22"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="D78" s="18"/>
+      <c r="D78" s="22"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="D79" s="18"/>
+      <c r="D79" s="22"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="D80" s="18"/>
+      <c r="D80" s="22"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="D81" s="18"/>
+      <c r="D81" s="22"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="D82" s="18"/>
+      <c r="D82" s="22"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="D83" s="18"/>
+      <c r="D83" s="22"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="D84" s="18"/>
+      <c r="D84" s="22"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="D85" s="18"/>
+      <c r="D85" s="22"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="D86" s="18"/>
+      <c r="D86" s="22"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="D87" s="18"/>
+      <c r="D87" s="22"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="D88" s="18"/>
+      <c r="D88" s="22"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="D89" s="18"/>
+      <c r="D89" s="22"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="D90" s="18"/>
+      <c r="D90" s="22"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="D91" s="18"/>
+      <c r="D91" s="22"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="D92" s="18"/>
+      <c r="D92" s="22"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="D93" s="18"/>
+      <c r="D93" s="22"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="D94" s="18"/>
+      <c r="D94" s="22"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="D95" s="18"/>
+      <c r="D95" s="22"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="D96" s="18"/>
+      <c r="D96" s="22"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="D97" s="18"/>
+      <c r="D97" s="22"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="D98" s="18"/>
+      <c r="D98" s="22"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="D99" s="18"/>
+      <c r="D99" s="22"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="D100" s="18"/>
+      <c r="D100" s="22"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="D101" s="18"/>
+      <c r="D101" s="22"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="D102" s="18"/>
+      <c r="D102" s="22"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="D103" s="18"/>
+      <c r="D103" s="22"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="D104" s="18"/>
+      <c r="D104" s="22"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="D105" s="18"/>
+      <c r="D105" s="22"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="D106" s="18"/>
+      <c r="D106" s="22"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="D107" s="18"/>
+      <c r="D107" s="22"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="D108" s="18"/>
+      <c r="D108" s="22"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="D109" s="18"/>
+      <c r="D109" s="22"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="D110" s="18"/>
+      <c r="D110" s="22"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="D111" s="18"/>
+      <c r="D111" s="22"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="D112" s="18"/>
+      <c r="D112" s="22"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="D113" s="18"/>
+      <c r="D113" s="22"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="D114" s="18"/>
+      <c r="D114" s="22"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="D115" s="18"/>
+      <c r="D115" s="22"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="D116" s="18"/>
+      <c r="D116" s="22"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="D117" s="18"/>
+      <c r="D117" s="22"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="D118" s="18"/>
+      <c r="D118" s="22"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="D119" s="18"/>
+      <c r="D119" s="22"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="D120" s="18"/>
+      <c r="D120" s="22"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="D121" s="18"/>
+      <c r="D121" s="22"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="D122" s="18"/>
+      <c r="D122" s="22"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="D123" s="18"/>
+      <c r="D123" s="22"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="D124" s="18"/>
+      <c r="D124" s="22"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="D125" s="18"/>
+      <c r="D125" s="22"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="D126" s="18"/>
+      <c r="D126" s="22"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="D127" s="18"/>
+      <c r="D127" s="22"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="D128" s="18"/>
+      <c r="D128" s="22"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="D129" s="18"/>
+      <c r="D129" s="22"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="D130" s="18"/>
+      <c r="D130" s="22"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="D131" s="18"/>
+      <c r="D131" s="22"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="D132" s="18"/>
+      <c r="D132" s="22"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="D133" s="18"/>
+      <c r="D133" s="22"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="D134" s="18"/>
+      <c r="D134" s="22"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="D135" s="18"/>
+      <c r="D135" s="22"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="D136" s="18"/>
+      <c r="D136" s="22"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="D137" s="18"/>
+      <c r="D137" s="22"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="D138" s="18"/>
+      <c r="D138" s="22"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="D139" s="18"/>
+      <c r="D139" s="22"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="D140" s="18"/>
+      <c r="D140" s="22"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="D141" s="18"/>
+      <c r="D141" s="22"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="D142" s="18"/>
+      <c r="D142" s="22"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="D143" s="18"/>
+      <c r="D143" s="22"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="D144" s="18"/>
+      <c r="D144" s="22"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="D145" s="18"/>
+      <c r="D145" s="22"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="D146" s="18"/>
+      <c r="D146" s="22"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="D147" s="18"/>
+      <c r="D147" s="22"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="D148" s="18"/>
+      <c r="D148" s="22"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="D149" s="18"/>
+      <c r="D149" s="22"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="D150" s="18"/>
+      <c r="D150" s="22"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="D151" s="18"/>
+      <c r="D151" s="22"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="D152" s="18"/>
+      <c r="D152" s="22"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="D153" s="18"/>
+      <c r="D153" s="22"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="D154" s="18"/>
+      <c r="D154" s="22"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="D155" s="18"/>
+      <c r="D155" s="22"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="D156" s="18"/>
+      <c r="D156" s="22"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="D157" s="18"/>
+      <c r="D157" s="22"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="D158" s="18"/>
+      <c r="D158" s="22"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="D159" s="18"/>
+      <c r="D159" s="22"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="D160" s="18"/>
+      <c r="D160" s="22"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="D161" s="18"/>
+      <c r="D161" s="22"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="D162" s="18"/>
+      <c r="D162" s="22"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="D163" s="18"/>
+      <c r="D163" s="22"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="D164" s="18"/>
+      <c r="D164" s="22"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="D165" s="18"/>
+      <c r="D165" s="22"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="D166" s="18"/>
+      <c r="D166" s="22"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="D167" s="18"/>
+      <c r="D167" s="22"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="D168" s="18"/>
+      <c r="D168" s="22"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="D169" s="18"/>
+      <c r="D169" s="22"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="D170" s="18"/>
+      <c r="D170" s="22"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="D171" s="18"/>
+      <c r="D171" s="22"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="D172" s="18"/>
+      <c r="D172" s="22"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="D173" s="18"/>
+      <c r="D173" s="22"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="D174" s="18"/>
+      <c r="D174" s="22"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="D175" s="18"/>
+      <c r="D175" s="22"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="D176" s="18"/>
+      <c r="D176" s="22"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="D177" s="18"/>
+      <c r="D177" s="22"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="D178" s="18"/>
+      <c r="D178" s="22"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="D179" s="18"/>
+      <c r="D179" s="22"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="D180" s="18"/>
+      <c r="D180" s="22"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="D181" s="18"/>
+      <c r="D181" s="22"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="D182" s="18"/>
+      <c r="D182" s="22"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="D183" s="18"/>
+      <c r="D183" s="22"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="D184" s="18"/>
+      <c r="D184" s="22"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="D185" s="18"/>
+      <c r="D185" s="22"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="D186" s="18"/>
+      <c r="D186" s="22"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="D187" s="18"/>
+      <c r="D187" s="22"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="D188" s="18"/>
+      <c r="D188" s="22"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="D189" s="18"/>
+      <c r="D189" s="22"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="D190" s="18"/>
+      <c r="D190" s="22"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="D191" s="18"/>
+      <c r="D191" s="22"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="D192" s="18"/>
+      <c r="D192" s="22"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="D193" s="18"/>
+      <c r="D193" s="22"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="D194" s="18"/>
+      <c r="D194" s="22"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="D195" s="18"/>
+      <c r="D195" s="22"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="D196" s="18"/>
+      <c r="D196" s="22"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="D197" s="18"/>
+      <c r="D197" s="22"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="D198" s="18"/>
+      <c r="D198" s="22"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="D199" s="18"/>
+      <c r="D199" s="22"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="D200" s="18"/>
+      <c r="D200" s="22"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="D201" s="18"/>
+      <c r="D201" s="22"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="D202" s="18"/>
+      <c r="D202" s="22"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="D203" s="18"/>
+      <c r="D203" s="22"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="D204" s="18"/>
+      <c r="D204" s="22"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="D205" s="18"/>
+      <c r="D205" s="22"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="D206" s="18"/>
+      <c r="D206" s="22"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="D207" s="18"/>
+      <c r="D207" s="22"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="D208" s="18"/>
+      <c r="D208" s="22"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="D209" s="18"/>
+      <c r="D209" s="22"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="D210" s="18"/>
+      <c r="D210" s="22"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="D211" s="18"/>
+      <c r="D211" s="22"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="D212" s="18"/>
+      <c r="D212" s="22"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="D213" s="18"/>
+      <c r="D213" s="22"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="D214" s="18"/>
+      <c r="D214" s="22"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="D215" s="18"/>
+      <c r="D215" s="22"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="D216" s="18"/>
+      <c r="D216" s="22"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="D217" s="18"/>
+      <c r="D217" s="22"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="D218" s="18"/>
+      <c r="D218" s="22"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="D219" s="18"/>
+      <c r="D219" s="22"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="D220" s="18"/>
+      <c r="D220" s="22"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
@@ -8531,228 +9113,228 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="10">
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="13">
         <v>-21.25</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="13">
         <v>-70.35</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="10">
+      <c r="G4" s="1"/>
+      <c r="H4" s="13">
         <v>-33.35</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="13">
         <v>-71.85</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="10">
+      <c r="G5" s="1"/>
+      <c r="H5" s="13">
         <v>-36.0</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="13">
         <v>-73.1</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="J5" s="13" t="s">
         <v>99</v>
       </c>
+      <c r="K5" s="13" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="10">
+      <c r="F6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="13">
         <v>-23.35</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="13">
         <v>-70.65</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>103</v>
+      <c r="K6" s="13" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="24" t="s">
+      <c r="E7" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="10">
+      <c r="F7" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="13">
         <v>-39.25</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="13">
         <v>-73.4</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>106</v>
+      <c r="J7" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -9760,146 +10342,240 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="42.0"/>
+    <col customWidth="1" min="6" max="6" width="14.0"/>
+    <col customWidth="1" min="7" max="7" width="12.0"/>
     <col customWidth="1" min="8" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="11" width="58.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="1">
+      <c r="B3" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="D3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11">
+        <v>-29.8</v>
+      </c>
+      <c r="I3" s="11">
+        <v>-71.5</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" ht="15.0" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="D4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11">
+        <v>-33.2</v>
+      </c>
+      <c r="I4" s="11">
+        <v>-71.4</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" ht="15.0" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="D5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11">
+        <v>-34.4</v>
+      </c>
+      <c r="I5" s="11">
+        <v>-72.3</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" ht="24.0" customHeight="1">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="D6" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="11">
+        <v>-23.4</v>
+      </c>
+      <c r="I6" s="11">
+        <v>-70.2</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" ht="15.0" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="D7" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="11">
+        <v>-41.6</v>
+      </c>
+      <c r="I7" s="11">
+        <v>-72.9</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -10907,146 +11583,240 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="42.0"/>
+    <col customWidth="1" min="6" max="6" width="14.0"/>
+    <col customWidth="1" min="7" max="7" width="12.0"/>
     <col customWidth="1" min="8" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="11" width="58.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="24.0" customHeight="1">
+      <c r="B3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="D3" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11">
+        <v>-22.91</v>
+      </c>
+      <c r="I3" s="11">
+        <v>-68.2</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" ht="24.0" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="D4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11">
+        <v>-27.45</v>
+      </c>
+      <c r="I4" s="11">
+        <v>-71.4</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" ht="15.0" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="D5" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11">
+        <v>-29.9</v>
+      </c>
+      <c r="I5" s="11">
+        <v>-71.6</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" ht="24.0" customHeight="1">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="D6" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="11">
+        <v>-20.48</v>
+      </c>
+      <c r="I6" s="11">
+        <v>-69.33</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" ht="15.0" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="D7" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="11">
+        <v>-33.05</v>
+      </c>
+      <c r="I7" s="11">
+        <v>-72.0</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -12054,146 +12824,240 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="42.0"/>
+    <col customWidth="1" min="6" max="6" width="14.0"/>
+    <col customWidth="1" min="7" max="7" width="12.0"/>
     <col customWidth="1" min="8" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="11" width="58.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="1">
+      <c r="B3" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="D3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11">
+        <v>-21.4</v>
+      </c>
+      <c r="I3" s="11">
+        <v>-68.6</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" ht="24.0" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="D4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11">
+        <v>-23.2</v>
+      </c>
+      <c r="I4" s="11">
+        <v>-67.2</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" ht="24.0" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="D5" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11">
+        <v>-22.5</v>
+      </c>
+      <c r="I5" s="11">
+        <v>-67.1</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" ht="24.0" customHeight="1">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="D6" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="11">
+        <v>-23.15</v>
+      </c>
+      <c r="I6" s="11">
+        <v>-70.55</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" ht="24.0" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="D7" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="11">
+        <v>-22.9</v>
+      </c>
+      <c r="I7" s="11">
+        <v>-70.7</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -13201,146 +14065,240 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="42.0"/>
+    <col customWidth="1" min="6" max="6" width="14.0"/>
+    <col customWidth="1" min="7" max="7" width="12.0"/>
     <col customWidth="1" min="8" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="11" width="58.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="1">
+      <c r="B3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="1">
         <v>1.0</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="4">
+      <c r="D3" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11">
+        <v>-20.5</v>
+      </c>
+      <c r="I3" s="11">
+        <v>-69.3</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" ht="15.0" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="4">
+      <c r="D4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11">
+        <v>-23.8</v>
+      </c>
+      <c r="I4" s="11">
+        <v>-68.1</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" ht="15.0" customHeight="1">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="11"/>
-      <c r="C6" s="4">
+      <c r="D5" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="11">
+        <v>-32.9</v>
+      </c>
+      <c r="I5" s="11">
+        <v>-71.8</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" ht="15.0" customHeight="1">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="4">
+      <c r="D6" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="11">
+        <v>-27.1</v>
+      </c>
+      <c r="I6" s="11">
+        <v>-70.9</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" ht="15.0" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="D7" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="11">
+        <v>-37.2</v>
+      </c>
+      <c r="I7" s="11">
+        <v>-73.6</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="11"/>
-      <c r="C8" s="4">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1">
         <v>6.0</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="11"/>
-      <c r="C9" s="4">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1">
         <v>7.0</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="11"/>
-      <c r="C10" s="4">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1">
         <v>8.0</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="11"/>
-      <c r="C11" s="4">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1">
         <v>9.0</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="4">
+      <c r="B12" s="20"/>
+      <c r="C12" s="1">
         <v>10.0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>

--- a/Proyecto_Tabla_de_datos_con_coordenadas.xlsx
+++ b/Proyecto_Tabla_de_datos_con_coordenadas.xlsx
@@ -2,17 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRUEBA" sheetId="1" r:id="Rb5ce8e1f4a3b429f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GROK" sheetId="2" r:id="R593c51e5ebff47b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEEPSEEK" sheetId="3" r:id="R119882990da8448e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHATGPT" sheetId="4" r:id="R10beb8d8b7c0437c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLAUDE" sheetId="5" r:id="R4846566832704051"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERPLEXITY" sheetId="6" r:id="R4ca934a67cdb4a87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META AI" sheetId="7" r:id="Rc7da6b9e45c44fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MISTRAL AI" sheetId="8" r:id="R004dbc3715bd4632"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMINI" sheetId="9" r:id="R42d18a85b14745df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COPILOT" sheetId="10" r:id="Reecd62399d114db9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QWEN" sheetId="11" r:id="Rc329e8ef8769464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRUEBA" sheetId="1" r:id="Rb7724335ba324e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GROK" sheetId="2" r:id="R142ebc71630a4571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEEPSEEK" sheetId="3" r:id="Rf7ae5cf6407b46ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHATGPT" sheetId="4" r:id="R5dcbe6e2d773434a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLAUDE" sheetId="5" r:id="Re2c168eb8e9d4e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERPLEXITY" sheetId="6" r:id="R90660a673da64359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META AI" sheetId="7" r:id="Rbb30deb1a6e547e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MISTRAL AI" sheetId="8" r:id="Rc501871970bb4d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMINI" sheetId="9" r:id="R137adff7c05243a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COPILOT" sheetId="10" r:id="Rc0c5b56266c44d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QWEN" sheetId="11" r:id="R05c40cd4f3f34a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 1" sheetId="12" r:id="R16e2812486744b2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,6 +21,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t xml:space="preserve">  ,</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">PRUEBA</x:t>
   </x:si>
   <x:si>
@@ -218,6 +222,36 @@
     <x:t xml:space="preserve">Centro aproximado La Serena–Coquimbo–Ovalle</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">2-4 de octubre 2026,</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Entorno de Calama / NE de Antofagasta (región de Antofagasta)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3.0 – 3.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona de Camiña / Collahuasi (región de Tarapacá)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Offshore o cerca de San Antonio / Navidad (región de O’Higgins – Valparaíso)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3.2 – 4.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Alrededores de La Higuera / Coquimbo (región de Coquimbo)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2.6 – 3.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NE de San Pedro de Atacama / Ollagüe (límite Antofagasta-Tarapacá)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2.9 – 3.7</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">DEEPSEEK</x:t>
   </x:si>
   <x:si>
@@ -281,349 +315,463 @@
     <x:t xml:space="preserve">Golfo de Arauco y península de Tumbes, zona de gran acoplamiento histórico</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">CHATGPT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10 - 13/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa de Tarapacá - Antofagasta</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4,0 - 5,0</x:t>
+    <x:t xml:space="preserve">2–4 de octubre de  2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Atacama–Coquimbo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4,0–5,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arica–Iquique–Antofagasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4,0–5,3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Valparaíso–Maule</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3,8–5,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Biobío–Los Lagos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3,5–4,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M6,0–7,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CLAUDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">11-13 sept, 00:00-06:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa Iquique-Tocopilla</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Franja costera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado Iquique–Tocopilla</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">11-13 sept, 12:00-18:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa Valparaíso-San Antonio</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado Valparaíso–San Antonio</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">11-13 sept, 06:00-12:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa Maule-Biobío</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.8</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Franja costera amplia</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Centro aproximado costa Tarapacá–Antofagasta</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa de Atacama - Coquimbo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3,5 - 4,8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado costa Atacama–Coquimbo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Valparaíso - O´Higgins</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3,5 - 4,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Franja regional amplia</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado Valparaíso–O'Higgins</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Maule - Araucanía</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3,5–4,7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado Maule–Araucanía</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Norte/centro de Chile, Antofagasta - Coquimbo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3,5–5,0</x:t>
+    <x:t xml:space="preserve">Centro aproximado costa Maule–Biobío</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">11-13 sept, 18:00-00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa Antofagasta-Mejillones</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado Antofagasta–Mejillones</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa Araucanía-Los Ríos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado costa Araucanía–Los Ríos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2-4 de octubre de 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interior de Antofagasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 3,5–4,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tarapacá (Iquique–Pica–Camiña</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 4,0–4,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Coquimbo–Valparaíso </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa centro-sur </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 3,5–4,3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arica–Antofagasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 5,0–5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PERPLEXITY</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09/2026, 11:00-14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">20-30 km al NO de La Serena, Coquimbo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4.0-4.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Subducción interplaca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona de falla activa; 4 sismos M4.0+ en septiembre de 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09/2026, 18:00-22:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">15-25 km al SE de Valparaíso, Valparaíso</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.5-4.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cercano a falla de San Ramón; zona central sísmicamente activa</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23/09/2026, 09:00-13:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">30-40 km al O de Pichilemu, O'Higgins</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.8-4.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona de ruptura del terremoto M8.8 de 2010; estrés tectónico residual</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23/09/2026, 20:00-23:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">25-35 km al NE de Antofagasta, Antofagasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.3-3.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Norte Grande; actividad sísmica constante por subducción de la placa de Nazca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24/09/2026, 06:00-10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10-20 km al S de Puerto Montt, Los Lagos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.6-4.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona sur; cercana a falla de Liquiñe-Ofqui; actividad volcánica asociada</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3–4/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interior de Antofagasta, entorno Calama–Ollagüe</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 2,5–3,7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Entre La Serena, Coquimbo e Illapel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 2,3–3,6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Océano Pacífico frente a San Antonio–Valparaíso</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 2,8–4,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cordillera de Biobío, entorno Antuco–Alto Biobío</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 2,6–4,1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interior de Tarapacá, al este/sureste de Iquique; zona Camiña–Huara</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M 2,4–3,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">META AI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09 18:00 a 24/09 08:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Antofagasta interior-San Pedro / Calama</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.8-4.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Intraplaca intermedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Placa de Nazca subductada a 100-130 km; eventos recientes en Mina Escondida y Ollagüe</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23/09 10:00 a 24/09 23:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Atacama costa-SO de Copiapó / Caldera offshore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.2-4.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interplaca somera-contacto</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Frente a la fosa; laguna sísmica de Atacama y acumulación de energía somera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09 20:00 a 23/09 22:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Coquimbo-O de La Serena offshore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.0-4.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Norte Chico; segundo peak nacional de sismicidad y actividad constante</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23/09 00:00 a 25/09 06:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tarapacá interior-E de Iquique / Pica</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3.5-4.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Subducción profunda bajo la Pampa del Tamarugal; sismos de 90-115 km frecuentes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09 22:00 a 24/09 18:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona Central-O de Valparaíso / San Antonio offshore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M2.8-3.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Segmento Los Vilos-Pichilemu; energía acumulada hacia la trinchera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MISTRAL AI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09/2026 00:00 – 24/09/2026 00:00 (48 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Valparaíso</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M5.0–6.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona costera de referencia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Valparaíso, Región de Valparaíso. Hipótesis basada en actividad histórica en la zona central; ventana de 48 horas.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23/09/2026 06:00 – 26/09/2026 06:00 (72 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Concepción</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4.8–5.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Concepción, Región del Biobío. Mistral menciona la falla de Pichilemu como supuesto; no se verifica relación geográfica con Concepción.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24/09/2026 12:00 – 27/09/2026 00:00 (60 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Iquique</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M5.5–6.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Iquique, Región de Tarapacá. Estimación experimental para el Norte Grande; ventana de 60 horas.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">25/09/2026 18:00 – 28/09/2026 00:00 (54 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Puerto Montt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4.5–5.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona sur de referencia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Puerto Montt, Región de Los Lagos. Mistral señala zona de subducción sur; ventana de 54 horas.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26/09/2026 03:00 – 28/09/2026 23:00 (68 h; fuente indica 70 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Copiapó</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M5.2–6.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zona interior de referencia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Copiapó, Región de Atacama. Hipótesis de actividad en el desierto de Atacama. Las horas indicadas suman 68 h, aunque Mistral escribió 70 h.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GEMINI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09/2026 09:15 UTC (24 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tarapacá, interior de Pica</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mw 3.8-4.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Intraplaca intermedia-profunda</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Alta recurrencia de sismicidad intraplaca intermedia a profunda</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22/09/2026 21:40 UTC (24 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Antofagasta, Socaire / Cordillera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mw 4.0-4.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Plano de subducción profundo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Frecuente liberación de energía en el plano de subducción a más de 100 km</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23/09/2026 14:10 UTC (48 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa de Valparaíso offshore</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mw 3.2-3.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interplaca somera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sismicidad interplaca menor continua debido al acoplamiento de placas</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23/09/2026 22:25 UTC (48 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Atacama, costa de Caldera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mw 3.5-4.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interplaca costera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Liberaciones menores habituales en el segmento costero</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24/09/2026 18:05 UTC (72 h)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Biobío, península de Arauco</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mw 3.0-3.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Interplaca / placa superior</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reajuste cortical postsísmico y deformación continua de la placa superior</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">COPILOT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10-13 de septiembre</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Región de Coquimbo y Antofagasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">4.0/5.5</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Macro-zona</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado Antofagasta–Coquimbo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CLAUDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">11-13 sept, 00:00-06:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa Iquique-Tocopilla</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Franja costera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado Iquique–Tocopilla</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">11-13 sept, 12:00-18:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa Valparaíso-San Antonio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado Valparaíso–San Antonio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">11-13 sept, 06:00-12:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa Maule-Biobío</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado costa Maule–Biobío</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">11-13 sept, 18:00-00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa Antofagasta-Mejillones</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado Antofagasta–Mejillones</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa Araucanía-Los Ríos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Centro aproximado costa Araucanía–Los Ríos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PERPLEXITY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22/09/2026, 11:00-14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">20-30 km al NO de La Serena, Coquimbo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M4.0-4.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Subducción interplaca</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zona de falla activa; 4 sismos M4.0+ en septiembre de 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22/09/2026, 18:00-22:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">15-25 km al SE de Valparaíso, Valparaíso</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.5-4.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cercano a falla de San Ramón; zona central sísmicamente activa</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23/09/2026, 09:00-13:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">30-40 km al O de Pichilemu, O'Higgins</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.8-4.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zona de ruptura del terremoto M8.8 de 2010; estrés tectónico residual</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23/09/2026, 20:00-23:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">25-35 km al NE de Antofagasta, Antofagasta</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.3-3.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Norte Grande; actividad sísmica constante por subducción de la placa de Nazca</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24/09/2026, 06:00-10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10-20 km al S de Puerto Montt, Los Lagos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.6-4.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zona sur; cercana a falla de Liquiñe-Ofqui; actividad volcánica asociada</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">META AI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22/09 18:00 a 24/09 08:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Antofagasta interior-San Pedro / Calama</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.8-4.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intraplaca intermedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Placa de Nazca subductada a 100-130 km; eventos recientes en Mina Escondida y Ollagüe</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23/09 10:00 a 24/09 23:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Atacama costa-SO de Copiapó / Caldera offshore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.2-4.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Interplaca somera-contacto</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Frente a la fosa; laguna sísmica de Atacama y acumulación de energía somera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22/09 20:00 a 23/09 22:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coquimbo-O de La Serena offshore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.0-4.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Norte Chico; segundo peak nacional de sismicidad y actividad constante</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23/09 00:00 a 25/09 06:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tarapacá interior-E de Iquique / Pica</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M3.5-4.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Subducción profunda bajo la Pampa del Tamarugal; sismos de 90-115 km frecuentes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22/09 22:00 a 24/09 18:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zona Central-O de Valparaíso / San Antonio offshore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M2.8-3.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Segmento Los Vilos-Pichilemu; energía acumulada hacia la trinchera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GEMINI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22/09/2026 09:15 UTC (24 h)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tarapacá, interior de Pica</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mw 3.8-4.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intraplaca intermedia-profunda</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Alta recurrencia de sismicidad intraplaca intermedia a profunda</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22/09/2026 21:40 UTC (24 h)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Antofagasta, Socaire / Cordillera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mw 4.0-4.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Plano de subducción profundo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Frecuente liberación de energía en el plano de subducción a más de 100 km</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23/09/2026 14:10 UTC (48 h)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Costa de Valparaíso offshore</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mw 3.2-3.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Interplaca somera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sismicidad interplaca menor continua debido al acoplamiento de placas</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23/09/2026 22:25 UTC (48 h)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Atacama, costa de Caldera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mw 3.5-4.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Interplaca costera</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Liberaciones menores habituales en el segmento costero</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24/09/2026 18:05 UTC (72 h)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Biobío, península de Arauco</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mw 3.0-3.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Interplaca / placa superior</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reajuste cortical postsísmico y deformación continua de la placa superior</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">COPILOT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10-13 de septiembre</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Región de Coquimbo y Antofagasta</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">4.0/5.5</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Centro aproximado entre ambas regiones</x:t>
@@ -738,13 +886,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy hh:mm"/>
+    <x:numFmt numFmtId="201" formatCode="0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
     <x:font>
@@ -767,11 +922,26 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
-    <x:font/>
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
+    </x:font>
+    <x:font/>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0F1115"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0F1115"/>
+      <x:name val="Quote-cjk-patch"/>
     </x:font>
     <x:font>
       <x:sz val="12"/>
@@ -779,17 +949,28 @@
       <x:name val="Arial"/>
     </x:font>
     <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF111111"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="lightGray"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -852,71 +1033,242 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="94">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="left" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="left" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1127,220 +1479,224 @@
     <x:col min="12" max="12" width="38" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15.75" customHeight="1"/>
+    <x:row r="1" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
     <x:row r="2" ht="15.75" customHeight="1">
-      <x:c r="B2" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="B2" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="s">
+      <x:c r="C2" s="4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="4" t="s">
+      <x:c r="D2" s="4" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G2" s="4" t="s">
+      <x:c r="F2" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H2" s="4" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="H2" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
-      <x:c r="B3" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="8">
+      <x:c r="B3" s="8" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="10">
         <x:v>46275.0</x:v>
       </x:c>
-      <x:c r="E3" s="10">
+      <x:c r="E3" s="12">
         <x:v>0.5625</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
+      <x:c r="F3" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="s">
+      <x:c r="G3" s="15" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I3" s="13">
+      <x:c r="H3" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I3" s="16">
         <x:v>-33.05</x:v>
       </x:c>
-      <x:c r="J3" s="13">
+      <x:c r="J3" s="16">
         <x:v>-71.85</x:v>
       </x:c>
-      <x:c r="K3" s="13" t="s">
+      <x:c r="K3" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L3" s="16" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15.75" customHeight="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D4" s="10">
+        <x:v>46275.0</x:v>
+      </x:c>
+      <x:c r="E4" s="12">
+        <x:v>0.5868055555555556</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G4" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H4" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L3" s="13" t="s">
+      <x:c r="I4" s="16">
+        <x:v>-29.95</x:v>
+      </x:c>
+      <x:c r="J4" s="16">
+        <x:v>-71.55</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="15.75" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D4" s="8">
+      <x:c r="L4" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15.75" customHeight="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="10">
         <x:v>46275.0</x:v>
       </x:c>
-      <x:c r="E4" s="10">
-        <x:v>0.5868055555555556</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G4" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H4" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I4" s="13">
-        <x:v>-29.95</x:v>
-      </x:c>
-      <x:c r="J4" s="13">
-        <x:v>-71.55</x:v>
-      </x:c>
-      <x:c r="K4" s="13" t="s">
+      <x:c r="E5" s="12">
+        <x:v>0.6111111111111112</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H5" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I5" s="16">
+        <x:v>-23.65</x:v>
+      </x:c>
+      <x:c r="J5" s="16">
+        <x:v>-70.65</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L5" s="16" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15.75" customHeight="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D6" s="10">
+        <x:v>46275.0</x:v>
+      </x:c>
+      <x:c r="E6" s="12">
+        <x:v>0.6388888888888888</x:v>
+      </x:c>
+      <x:c r="F6" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G6" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H6" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I6" s="16">
+        <x:v>-20.2</x:v>
+      </x:c>
+      <x:c r="J6" s="16">
+        <x:v>-70.4</x:v>
+      </x:c>
+      <x:c r="K6" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L6" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15.75" customHeight="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D7" s="10">
+        <x:v>46275.0</x:v>
+      </x:c>
+      <x:c r="E7" s="12">
+        <x:v>0.6631944444444444</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G7" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H7" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L4" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="15.75" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D5" s="8">
-        <x:v>46275.0</x:v>
-      </x:c>
-      <x:c r="E5" s="10">
-        <x:v>0.6111111111111112</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G5" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H5" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="I5" s="13">
-        <x:v>-23.65</x:v>
-      </x:c>
-      <x:c r="J5" s="13">
-        <x:v>-70.65</x:v>
-      </x:c>
-      <x:c r="K5" s="13" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L5" s="13" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15.75" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D6" s="8">
-        <x:v>46275.0</x:v>
-      </x:c>
-      <x:c r="E6" s="10">
-        <x:v>0.6388888888888888</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G6" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H6" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>-20.2</x:v>
-      </x:c>
-      <x:c r="J6" s="13">
-        <x:v>-70.4</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L6" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15.75" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="8">
-        <x:v>46275.0</x:v>
-      </x:c>
-      <x:c r="E7" s="10">
-        <x:v>0.6631944444444444</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G7" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H7" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="I7" s="16">
         <x:v>-27.37</x:v>
       </x:c>
-      <x:c r="J7" s="13">
+      <x:c r="J7" s="16">
         <x:v>-70.33</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="K7" s="16" t="s">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="L7" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="17"/>
+      <x:c r="B8" s="23"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="19"/>
+      <x:c r="B9" s="27"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="19"/>
+      <x:c r="B10" s="27"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="19"/>
+      <x:c r="B11" s="27"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1"/>
     <x:row r="13" ht="15.75" customHeight="1"/>
@@ -2355,227 +2711,227 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="E3" s="24" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F3" s="24" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="13">
+      <x:c r="D3" s="3" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="E3" s="33" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F3" s="33" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="16">
         <x:v>-26.8</x:v>
       </x:c>
-      <x:c r="I3" s="13">
+      <x:c r="I3" s="16">
         <x:v>-70.5</x:v>
       </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="K3" s="13" t="s">
-        <x:v>202</x:v>
+      <x:c r="J3" s="16" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K3" s="16" t="s">
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15.75" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="E4" s="24" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F4" s="24" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="13">
+      <x:c r="D4" s="3" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="E4" s="33" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="F4" s="33" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G4" s="3"/>
+      <x:c r="H4" s="16">
         <x:v>-37.8</x:v>
       </x:c>
-      <x:c r="I4" s="13">
+      <x:c r="I4" s="16">
         <x:v>-72.6</x:v>
       </x:c>
-      <x:c r="J4" s="13" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="K4" s="13" t="s">
-        <x:v>205</x:v>
+      <x:c r="J4" s="16" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="s">
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15.75" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="E5" s="24" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F5" s="24" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G5" s="1"/>
-      <x:c r="H5" s="13">
+      <x:c r="D5" s="3" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="E5" s="33" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F5" s="33" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G5" s="3"/>
+      <x:c r="H5" s="16">
         <x:v>-45.57</x:v>
       </x:c>
-      <x:c r="I5" s="13">
+      <x:c r="I5" s="16">
         <x:v>-72.07</x:v>
       </x:c>
-      <x:c r="J5" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K5" s="13" t="s">
-        <x:v>208</x:v>
+      <x:c r="J5" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="s">
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15.75" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
         <x:v>4.0</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="E6" s="24" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F6" s="24" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G6" s="1"/>
-      <x:c r="H6" s="13">
+      <x:c r="D6" s="3" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="E6" s="33" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F6" s="33" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="16">
         <x:v>-33.3</x:v>
       </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="I6" s="16">
         <x:v>-71.0</x:v>
       </x:c>
-      <x:c r="J6" s="13" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="s">
-        <x:v>211</x:v>
+      <x:c r="J6" s="16" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K6" s="16" t="s">
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15.75" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
         <x:v>5.0</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="E7" s="24" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F7" s="24" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G7" s="1"/>
-      <x:c r="H7" s="13">
+      <x:c r="D7" s="3" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="E7" s="33" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F7" s="33" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="16">
         <x:v>-19.4</x:v>
       </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="I7" s="16">
         <x:v>-69.8</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="s">
-        <x:v>213</x:v>
+      <x:c r="J7" s="16" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K7" s="16" t="s">
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="3"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -3590,227 +3946,227 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="G3" s="9"/>
-      <x:c r="H3" s="11">
+      <x:c r="D3" s="19" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G3" s="19"/>
+      <x:c r="H3" s="20">
         <x:v>-21.5</x:v>
       </x:c>
-      <x:c r="I3" s="11">
+      <x:c r="I3" s="20">
         <x:v>-68.5</x:v>
       </x:c>
-      <x:c r="J3" s="11" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="s">
-        <x:v>219</x:v>
+      <x:c r="J3" s="20" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="s">
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G4" s="9"/>
-      <x:c r="H4" s="11">
+      <x:c r="D4" s="19" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="E4" s="19" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F4" s="19" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G4" s="19"/>
+      <x:c r="H4" s="20">
         <x:v>-23.0</x:v>
       </x:c>
-      <x:c r="I4" s="11">
+      <x:c r="I4" s="20">
         <x:v>-70.8</x:v>
       </x:c>
-      <x:c r="J4" s="11" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="s">
-        <x:v>223</x:v>
+      <x:c r="J4" s="20" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="s">
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="11">
+      <x:c r="D5" s="19" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G5" s="19"/>
+      <x:c r="H5" s="20">
         <x:v>-34.2</x:v>
       </x:c>
-      <x:c r="I5" s="11">
+      <x:c r="I5" s="20">
         <x:v>-70.7</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="K5" s="11" t="s">
-        <x:v>228</x:v>
+      <x:c r="J5" s="20" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="s">
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
         <x:v>4.0</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G6" s="9"/>
-      <x:c r="H6" s="11">
+      <x:c r="D6" s="19" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20">
         <x:v>-40.0</x:v>
       </x:c>
-      <x:c r="I6" s="11">
+      <x:c r="I6" s="20">
         <x:v>-72.5</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="s">
-        <x:v>233</x:v>
+      <x:c r="J6" s="20" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="s">
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
         <x:v>5.0</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="11">
+      <x:c r="D7" s="19" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G7" s="19"/>
+      <x:c r="H7" s="20">
         <x:v>-46.5</x:v>
       </x:c>
-      <x:c r="I7" s="11">
+      <x:c r="I7" s="20">
         <x:v>-74.5</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="K7" s="11" t="s">
-        <x:v>237</x:v>
+      <x:c r="J7" s="20" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="s">
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="3"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -4808,13 +5164,21 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15"/>
+  <x:sheetData/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="3" width="12.630000114440918" customWidth="1"/>
     <x:col min="4" max="4" width="16.6299991607666" customWidth="1"/>
-    <x:col min="5" max="5" width="45.5" customWidth="1"/>
+    <x:col min="5" max="5" width="58.5" customWidth="1"/>
     <x:col min="6" max="6" width="19.1299991607666" customWidth="1"/>
     <x:col min="8" max="9" width="13" customWidth="1"/>
     <x:col min="10" max="10" width="20" customWidth="1"/>
@@ -4824,235 +5188,265 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C3" s="2">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E3" s="16" t="s">
+      <x:c r="D3" s="9" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F3" s="18" t="s">
+      <x:c r="E3" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="F3" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="G3" s="2"/>
-      <x:c r="H3" s="13">
+      <x:c r="H3" s="16">
         <x:v>-21.9</x:v>
       </x:c>
-      <x:c r="I3" s="13">
+      <x:c r="I3" s="16">
         <x:v>-69.8</x:v>
       </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K3" s="13" t="s">
+      <x:c r="J3" s="16" t="s">
         <x:v>46</x:v>
       </x:c>
+      <x:c r="K3" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="15.75" customHeight="1">
-      <x:c r="B4" s="14"/>
+      <x:c r="B4" s="17"/>
       <x:c r="C4" s="2">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="s">
+      <x:c r="D4" s="9" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F4" s="18" t="s">
+      <x:c r="E4" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
+      <x:c r="F4" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="G4" s="2"/>
-      <x:c r="H4" s="13">
+      <x:c r="H4" s="16">
         <x:v>-21.95</x:v>
       </x:c>
-      <x:c r="I4" s="13">
+      <x:c r="I4" s="16">
         <x:v>-68.75</x:v>
       </x:c>
-      <x:c r="J4" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K4" s="13" t="s">
+      <x:c r="J4" s="16" t="s">
         <x:v>51</x:v>
       </x:c>
+      <x:c r="K4" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="15.75" customHeight="1">
-      <x:c r="B5" s="14"/>
+      <x:c r="B5" s="17"/>
       <x:c r="C5" s="2">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E5" s="15" t="s">
+      <x:c r="D5" s="9" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F5" s="18" t="s">
+      <x:c r="E5" s="9" t="s">
         <x:v>54</x:v>
       </x:c>
+      <x:c r="F5" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="G5" s="2"/>
-      <x:c r="H5" s="13">
+      <x:c r="H5" s="16">
         <x:v>-20.55</x:v>
       </x:c>
-      <x:c r="I5" s="13">
+      <x:c r="I5" s="16">
         <x:v>-69.25</x:v>
       </x:c>
-      <x:c r="J5" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K5" s="13" t="s">
-        <x:v>55</x:v>
+      <x:c r="J5" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15.75" customHeight="1">
-      <x:c r="B6" s="14"/>
+      <x:c r="B6" s="17"/>
       <x:c r="C6" s="2">
         <x:v>4.0</x:v>
       </x:c>
-      <x:c r="D6" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E6" s="15" t="s">
+      <x:c r="D6" s="9" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F6" s="15" t="s">
+      <x:c r="E6" s="9" t="s">
         <x:v>58</x:v>
       </x:c>
+      <x:c r="F6" s="9" t="s">
+        <x:v>59</x:v>
+      </x:c>
       <x:c r="G6" s="2"/>
-      <x:c r="H6" s="13">
+      <x:c r="H6" s="16">
         <x:v>-27.35</x:v>
       </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="I6" s="16">
         <x:v>-69.7</x:v>
       </x:c>
-      <x:c r="J6" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="s">
+      <x:c r="J6" s="16" t="s">
         <x:v>60</x:v>
       </x:c>
+      <x:c r="K6" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15.75" customHeight="1">
-      <x:c r="B7" s="14"/>
+      <x:c r="B7" s="17"/>
       <x:c r="C7" s="2">
         <x:v>5.0</x:v>
       </x:c>
-      <x:c r="D7" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E7" s="15" t="s">
+      <x:c r="D7" s="9" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F7" s="15" t="s">
+      <x:c r="E7" s="9" t="s">
         <x:v>63</x:v>
       </x:c>
+      <x:c r="F7" s="9" t="s">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="G7" s="2"/>
-      <x:c r="H7" s="13">
+      <x:c r="H7" s="16">
         <x:v>-30.2</x:v>
       </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="I7" s="16">
         <x:v>-71.15</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="J7" s="16" t="s">
         <x:v>65</x:v>
       </x:c>
+      <x:c r="K7" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
+      <x:c r="B8" s="17"/>
       <x:c r="C8" s="2">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="2"/>
-      <x:c r="E8" s="2"/>
-      <x:c r="F8" s="2"/>
+      <x:c r="D8" s="24" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="s">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="G8" s="2"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
+      <x:c r="B9" s="17"/>
       <x:c r="C9" s="2">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="2"/>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
+      <x:c r="D9" s="24" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E9" s="24" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F9" s="24" t="s">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="G9" s="2"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
+      <x:c r="B10" s="17"/>
       <x:c r="C10" s="2">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
+      <x:c r="D10" s="24" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F10" s="24" t="s">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="G10" s="2"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
+      <x:c r="B11" s="17"/>
       <x:c r="C11" s="2">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
+      <x:c r="D11" s="24" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E11" s="24" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="G11" s="2"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
+      <x:c r="B12" s="29"/>
       <x:c r="C12" s="2">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
+      <x:c r="D12" s="24" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F12" s="24" t="s">
+        <x:v>76</x:v>
+      </x:c>
       <x:c r="G12" s="2"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1">
-      <x:c r="B13" s="19"/>
-      <x:c r="C13" s="19"/>
-      <x:c r="D13" s="19"/>
-      <x:c r="E13" s="19"/>
-      <x:c r="F13" s="19"/>
-      <x:c r="G13" s="19"/>
+      <x:c r="B13" s="27"/>
+      <x:c r="C13" s="27"/>
+      <x:c r="D13" s="27"/>
+      <x:c r="E13" s="27"/>
+      <x:c r="F13" s="27"/>
+      <x:c r="G13" s="27"/>
     </x:row>
     <x:row r="14" ht="15.75" customHeight="1"/>
     <x:row r="15" ht="15.75" customHeight="1"/>
@@ -6066,227 +6460,257 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G3" s="9"/>
-      <x:c r="H3" s="11">
+      <x:c r="D3" s="19" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G3" s="19"/>
+      <x:c r="H3" s="20">
         <x:v>-23.5</x:v>
       </x:c>
-      <x:c r="I3" s="11">
+      <x:c r="I3" s="20">
         <x:v>-70.5</x:v>
       </x:c>
-      <x:c r="J3" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="s">
-        <x:v>71</x:v>
+      <x:c r="J3" s="20" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="s">
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G4" s="9"/>
-      <x:c r="H4" s="11">
+      <x:c r="D4" s="19" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E4" s="19" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F4" s="19" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G4" s="19"/>
+      <x:c r="H4" s="20">
         <x:v>-28.0</x:v>
       </x:c>
-      <x:c r="I4" s="11">
+      <x:c r="I4" s="20">
         <x:v>-70.8</x:v>
       </x:c>
-      <x:c r="J4" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="s">
-        <x:v>75</x:v>
+      <x:c r="J4" s="20" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="s">
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="11">
+      <x:c r="D5" s="19" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G5" s="19"/>
+      <x:c r="H5" s="20">
         <x:v>-30.0</x:v>
       </x:c>
-      <x:c r="I5" s="11">
+      <x:c r="I5" s="20">
         <x:v>-71.2</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="s">
+      <x:c r="J5" s="20" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
+        <x:v>4.0</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="K5" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
-        <x:v>4.0</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G6" s="9"/>
-      <x:c r="H6" s="11">
+      <x:c r="E6" s="19" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20">
         <x:v>-33.4</x:v>
       </x:c>
-      <x:c r="I6" s="11">
+      <x:c r="I6" s="20">
         <x:v>-70.3</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="s">
-        <x:v>83</x:v>
+      <x:c r="J6" s="20" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
         <x:v>5.0</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="11">
+      <x:c r="D7" s="19" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G7" s="19"/>
+      <x:c r="H7" s="20">
         <x:v>-36.8</x:v>
       </x:c>
-      <x:c r="I7" s="11">
+      <x:c r="I7" s="20">
         <x:v>-73.0</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="K7" s="11" t="s">
-        <x:v>86</x:v>
+      <x:c r="J7" s="20" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="25" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E8" s="28" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F8" s="28" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="25" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="25" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="25" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="25" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -7289,864 +7713,982 @@
   <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="3" width="12.630000114440918" customWidth="1"/>
-    <x:col min="4" max="4" width="13.880000114440918" customWidth="1"/>
-    <x:col min="5" max="5" width="40.5" customWidth="1"/>
-    <x:col min="6" max="6" width="9.75" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="9" width="13" customWidth="1"/>
-    <x:col min="10" max="10" width="20" customWidth="1"/>
-    <x:col min="11" max="11" width="38" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="21" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="21" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15.75" customHeight="1">
-      <x:c r="D1" s="22"/>
-    </x:row>
-    <x:row r="2" ht="15.75" customHeight="1">
+      <x:c r="D1" s="13"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="23" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="D2" s="18" t="str">
+        <x:v>Dia/Mes</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H2" s="68" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="68" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="68" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="68" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L2" s="68" t="str">
+        <x:v>Fecha estimada</x:v>
+      </x:c>
+      <x:c r="M2" s="68" t="str">
+        <x:v>Hora estimada</x:v>
+      </x:c>
+      <x:c r="N2" s="68" t="str">
+        <x:v>Inicio ventana</x:v>
+      </x:c>
+      <x:c r="O2" s="68" t="str">
+        <x:v>Fin ventana</x:v>
+      </x:c>
+      <x:c r="P2" s="68" t="str">
+        <x:v>Confianza</x:v>
+      </x:c>
+      <x:c r="Q2" s="68" t="str">
+        <x:v>Rango M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="34" customHeight="1">
+      <x:c r="B3" s="7" t="str">
+        <x:v>CHATGPT</x:v>
+      </x:c>
+      <x:c r="C3" s="84" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="85" t="str">
+        <x:v>02/10/2026 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E3" s="92" t="str">
+        <x:v>Costa de Antofagasta, entre Mejillones y Taltal</x:v>
+      </x:c>
+      <x:c r="F3" s="85" t="str">
+        <x:v>M4,0</x:v>
+      </x:c>
+      <x:c r="G3" s="84"/>
+      <x:c r="H3" s="86" t="n">
+        <x:v>-24.25</x:v>
+      </x:c>
+      <x:c r="I3" s="86" t="n">
+        <x:v>-70.75</x:v>
+      </x:c>
+      <x:c r="J3" s="93" t="str">
+        <x:v>Franja costera</x:v>
+      </x:c>
+      <x:c r="K3" s="93" t="str">
+        <x:v>Centro aproximado de la costa de Antofagasta, entre Mejillones y Taltal</x:v>
+      </x:c>
+      <x:c r="L3" s="88" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="M3" s="89" t="str">
+        <x:v>08:30</x:v>
+      </x:c>
+      <x:c r="N3" s="90" t="n">
+        <x:v>46297.833333333336</x:v>
+      </x:c>
+      <x:c r="O3" s="90" t="n">
+        <x:v>46299.833333333336</x:v>
+      </x:c>
+      <x:c r="P3" s="91" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="Q3" s="89" t="str">
+        <x:v>M3,5–4,5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="84" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="85" t="str">
+        <x:v>02/10/2026 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E4" s="82" t="str">
+        <x:v>Región de Tarapacá, zona Iquique–Pica</x:v>
+      </x:c>
+      <x:c r="F4" s="87" t="str">
+        <x:v>M3,7</x:v>
+      </x:c>
+      <x:c r="G4" s="84"/>
+      <x:c r="H4" s="86" t="n">
+        <x:v>-20.35</x:v>
+      </x:c>
+      <x:c r="I4" s="86" t="n">
+        <x:v>-69.8</x:v>
+      </x:c>
+      <x:c r="J4" s="93" t="str">
+        <x:v>Corredor costa–interior</x:v>
+      </x:c>
+      <x:c r="K4" s="93" t="str">
+        <x:v>Punto de referencia aproximado entre Iquique y Pica, Región de Tarapacá</x:v>
+      </x:c>
+      <x:c r="L4" s="88" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="M4" s="89" t="str">
+        <x:v>22:10</x:v>
+      </x:c>
+      <x:c r="N4" s="90" t="n">
+        <x:v>46297.416666666664</x:v>
+      </x:c>
+      <x:c r="O4" s="90" t="n">
+        <x:v>46299.416666666664</x:v>
+      </x:c>
+      <x:c r="P4" s="91" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="Q4" s="89" t="str">
+        <x:v>M3,2–4,2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="84" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D5" s="85" t="str">
+        <x:v>02/10/2026 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E5" s="92" t="str">
+        <x:v>Costa de Coquimbo, entre La Serena y Los Vilos</x:v>
+      </x:c>
+      <x:c r="F5" s="85" t="str">
+        <x:v>M4,2</x:v>
+      </x:c>
+      <x:c r="G5" s="84"/>
+      <x:c r="H5" s="86" t="n">
+        <x:v>-30.9</x:v>
+      </x:c>
+      <x:c r="I5" s="86" t="n">
+        <x:v>-71.5</x:v>
+      </x:c>
+      <x:c r="J5" s="93" t="str">
+        <x:v>Franja costera</x:v>
+      </x:c>
+      <x:c r="K5" s="93" t="str">
+        <x:v>Centro aproximado de la costa entre La Serena y Los Vilos</x:v>
+      </x:c>
+      <x:c r="L5" s="88" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="M5" s="89" t="str">
+        <x:v>15:40</x:v>
+      </x:c>
+      <x:c r="N5" s="90" t="n">
+        <x:v>46297.625</x:v>
+      </x:c>
+      <x:c r="O5" s="90" t="n">
+        <x:v>46299.958333333336</x:v>
+      </x:c>
+      <x:c r="P5" s="91" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="Q5" s="89" t="str">
+        <x:v>M3,7–4,7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="84" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="85" t="str">
+        <x:v>03/10/2026 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E6" s="92" t="str">
+        <x:v>Región de Atacama, zona Copiapó–Caldera</x:v>
+      </x:c>
+      <x:c r="F6" s="85" t="str">
+        <x:v>M3,8</x:v>
+      </x:c>
+      <x:c r="G6" s="84"/>
+      <x:c r="H6" s="86" t="n">
+        <x:v>-27.22</x:v>
+      </x:c>
+      <x:c r="I6" s="86" t="n">
+        <x:v>-70.58</x:v>
+      </x:c>
+      <x:c r="J6" s="93" t="str">
+        <x:v>Corredor costa–interior</x:v>
+      </x:c>
+      <x:c r="K6" s="93" t="str">
+        <x:v>Punto medio aproximado entre Copiapó y Caldera, Región de Atacama</x:v>
+      </x:c>
+      <x:c r="L6" s="88" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="M6" s="89" t="str">
+        <x:v>01:20</x:v>
+      </x:c>
+      <x:c r="N6" s="90" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="O6" s="90" t="n">
+        <x:v>46299.99930555555</x:v>
+      </x:c>
+      <x:c r="P6" s="91" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="Q6" s="89" t="str">
+        <x:v>M3,3–4,3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="84" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="15.75" customHeight="1">
-      <x:c r="B3" s="7" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="D3" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E3" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F3" s="23" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="13">
-        <x:v>-21.9</x:v>
-      </x:c>
-      <x:c r="I3" s="13">
-        <x:v>-70.35</x:v>
-      </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K3" s="13" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="15.75" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
-        <x:v>2.0</x:v>
-      </x:c>
-      <x:c r="D4" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E4" s="25" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F4" s="26" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="13">
-        <x:v>-28.9</x:v>
-      </x:c>
-      <x:c r="I4" s="13">
-        <x:v>-71.45</x:v>
-      </x:c>
-      <x:c r="J4" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K4" s="13" t="s">
-        <x:v>95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="15.75" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
-        <x:v>3.0</x:v>
-      </x:c>
-      <x:c r="D5" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E5" s="23" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F5" s="23" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G5" s="1"/>
-      <x:c r="H5" s="13">
-        <x:v>-33.8</x:v>
-      </x:c>
-      <x:c r="I5" s="13">
-        <x:v>-71.2</x:v>
-      </x:c>
-      <x:c r="J5" s="13" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="K5" s="13" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15.75" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
-        <x:v>4.0</x:v>
-      </x:c>
-      <x:c r="D6" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E6" s="23" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F6" s="23" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G6" s="1"/>
-      <x:c r="H6" s="13">
-        <x:v>-37.0</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>-72.2</x:v>
-      </x:c>
-      <x:c r="J6" s="13" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15.75" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
-        <x:v>5.0</x:v>
-      </x:c>
-      <x:c r="D7" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E7" s="23" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F7" s="23" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G7" s="1"/>
-      <x:c r="H7" s="13">
-        <x:v>-27.0</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>-70.6</x:v>
-      </x:c>
-      <x:c r="J7" s="13" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="s">
-        <x:v>106</x:v>
+      <x:c r="D7" s="85" t="str">
+        <x:v>02/10/2026 - 03/10/2026</x:v>
+      </x:c>
+      <x:c r="E7" s="92" t="str">
+        <x:v>Región de Valparaíso, frente a San Antonio</x:v>
+      </x:c>
+      <x:c r="F7" s="85" t="str">
+        <x:v>M3,6</x:v>
+      </x:c>
+      <x:c r="G7" s="84"/>
+      <x:c r="H7" s="86" t="n">
+        <x:v>-33.6</x:v>
+      </x:c>
+      <x:c r="I7" s="86" t="n">
+        <x:v>-72</x:v>
+      </x:c>
+      <x:c r="J7" s="93" t="str">
+        <x:v>Zona costera / mar adentro</x:v>
+      </x:c>
+      <x:c r="K7" s="93" t="str">
+        <x:v>Referencia aproximada mar adentro frente a San Antonio</x:v>
+      </x:c>
+      <x:c r="L7" s="88" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="M7" s="89" t="str">
+        <x:v>18:50</x:v>
+      </x:c>
+      <x:c r="N7" s="90" t="n">
+        <x:v>46297.25</x:v>
+      </x:c>
+      <x:c r="O7" s="90" t="n">
+        <x:v>46298.958333333336</x:v>
+      </x:c>
+      <x:c r="P7" s="91" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="Q7" s="89" t="str">
+        <x:v>M3,1–4,1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="23"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="18"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="23"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="18"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="23"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="18"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="23"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="18"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="23"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="18"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1">
-      <x:c r="D13" s="22"/>
+      <x:c r="D13" s="13"/>
     </x:row>
     <x:row r="14" ht="15.75" customHeight="1">
-      <x:c r="D14" s="22"/>
+      <x:c r="D14" s="13"/>
     </x:row>
     <x:row r="15" ht="15.75" customHeight="1">
-      <x:c r="D15" s="22"/>
+      <x:c r="D15" s="13"/>
     </x:row>
     <x:row r="16" ht="15.75" customHeight="1">
-      <x:c r="D16" s="22"/>
+      <x:c r="D16" s="13"/>
     </x:row>
     <x:row r="17" ht="15.75" customHeight="1">
-      <x:c r="D17" s="22"/>
+      <x:c r="D17" s="13"/>
     </x:row>
     <x:row r="18" ht="15.75" customHeight="1">
-      <x:c r="D18" s="22"/>
+      <x:c r="D18" s="13"/>
     </x:row>
     <x:row r="19" ht="15.75" customHeight="1">
-      <x:c r="D19" s="22"/>
+      <x:c r="D19" s="13"/>
     </x:row>
     <x:row r="20" ht="15.75" customHeight="1">
-      <x:c r="D20" s="22"/>
+      <x:c r="D20" s="13"/>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
-      <x:c r="D21" s="22"/>
+      <x:c r="D21" s="13"/>
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1">
-      <x:c r="D22" s="22"/>
+      <x:c r="D22" s="13"/>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
-      <x:c r="D23" s="22"/>
+      <x:c r="D23" s="13"/>
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
-      <x:c r="D24" s="22"/>
+      <x:c r="D24" s="13"/>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
-      <x:c r="D25" s="22"/>
+      <x:c r="D25" s="13"/>
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1">
-      <x:c r="D26" s="22"/>
+      <x:c r="D26" s="13"/>
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
-      <x:c r="D27" s="22"/>
+      <x:c r="D27" s="13"/>
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
-      <x:c r="D28" s="22"/>
+      <x:c r="D28" s="13"/>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
-      <x:c r="D29" s="22"/>
+      <x:c r="D29" s="13"/>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
-      <x:c r="D30" s="22"/>
+      <x:c r="D30" s="13"/>
     </x:row>
     <x:row r="31" ht="15.75" customHeight="1">
-      <x:c r="D31" s="22"/>
+      <x:c r="D31" s="13"/>
     </x:row>
     <x:row r="32" ht="15.75" customHeight="1">
-      <x:c r="D32" s="22"/>
+      <x:c r="D32" s="13"/>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
-      <x:c r="D33" s="22"/>
+      <x:c r="D33" s="13"/>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
-      <x:c r="D34" s="22"/>
+      <x:c r="D34" s="13"/>
     </x:row>
     <x:row r="35" ht="15.75" customHeight="1">
-      <x:c r="D35" s="22"/>
+      <x:c r="D35" s="13"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
-      <x:c r="D36" s="22"/>
+      <x:c r="D36" s="13"/>
     </x:row>
     <x:row r="37" ht="15.75" customHeight="1">
-      <x:c r="D37" s="22"/>
+      <x:c r="D37" s="13"/>
     </x:row>
     <x:row r="38" ht="15.75" customHeight="1">
-      <x:c r="D38" s="22"/>
+      <x:c r="D38" s="13"/>
     </x:row>
     <x:row r="39" ht="15.75" customHeight="1">
-      <x:c r="D39" s="22"/>
+      <x:c r="D39" s="13"/>
     </x:row>
     <x:row r="40" ht="15.75" customHeight="1">
-      <x:c r="D40" s="22"/>
+      <x:c r="D40" s="13"/>
     </x:row>
     <x:row r="41" ht="15.75" customHeight="1">
-      <x:c r="D41" s="22"/>
+      <x:c r="D41" s="13"/>
     </x:row>
     <x:row r="42" ht="15.75" customHeight="1">
-      <x:c r="D42" s="22"/>
+      <x:c r="D42" s="13"/>
     </x:row>
     <x:row r="43" ht="15.75" customHeight="1">
-      <x:c r="D43" s="22"/>
+      <x:c r="D43" s="13"/>
     </x:row>
     <x:row r="44" ht="15.75" customHeight="1">
-      <x:c r="D44" s="22"/>
+      <x:c r="D44" s="13"/>
     </x:row>
     <x:row r="45" ht="15.75" customHeight="1">
-      <x:c r="D45" s="22"/>
+      <x:c r="D45" s="13"/>
     </x:row>
     <x:row r="46" ht="15.75" customHeight="1">
-      <x:c r="D46" s="22"/>
+      <x:c r="D46" s="13"/>
     </x:row>
     <x:row r="47" ht="15.75" customHeight="1">
-      <x:c r="D47" s="22"/>
+      <x:c r="D47" s="13"/>
     </x:row>
     <x:row r="48" ht="15.75" customHeight="1">
-      <x:c r="D48" s="22"/>
+      <x:c r="D48" s="13"/>
     </x:row>
     <x:row r="49" ht="15.75" customHeight="1">
-      <x:c r="D49" s="22"/>
+      <x:c r="D49" s="13"/>
     </x:row>
     <x:row r="50" ht="15.75" customHeight="1">
-      <x:c r="D50" s="22"/>
+      <x:c r="D50" s="13"/>
     </x:row>
     <x:row r="51" ht="15.75" customHeight="1">
-      <x:c r="D51" s="22"/>
+      <x:c r="D51" s="13"/>
     </x:row>
     <x:row r="52" ht="15.75" customHeight="1">
-      <x:c r="D52" s="22"/>
+      <x:c r="D52" s="13"/>
     </x:row>
     <x:row r="53" ht="15.75" customHeight="1">
-      <x:c r="D53" s="22"/>
+      <x:c r="D53" s="13"/>
     </x:row>
     <x:row r="54" ht="15.75" customHeight="1">
-      <x:c r="D54" s="22"/>
+      <x:c r="D54" s="13"/>
     </x:row>
     <x:row r="55" ht="15.75" customHeight="1">
-      <x:c r="D55" s="22"/>
+      <x:c r="D55" s="13"/>
     </x:row>
     <x:row r="56" ht="15.75" customHeight="1">
-      <x:c r="D56" s="22"/>
+      <x:c r="D56" s="13"/>
     </x:row>
     <x:row r="57" ht="15.75" customHeight="1">
-      <x:c r="D57" s="22"/>
+      <x:c r="D57" s="13"/>
     </x:row>
     <x:row r="58" ht="15.75" customHeight="1">
-      <x:c r="D58" s="22"/>
+      <x:c r="D58" s="13"/>
     </x:row>
     <x:row r="59" ht="15.75" customHeight="1">
-      <x:c r="D59" s="22"/>
+      <x:c r="D59" s="13"/>
     </x:row>
     <x:row r="60" ht="15.75" customHeight="1">
-      <x:c r="D60" s="22"/>
+      <x:c r="D60" s="13"/>
     </x:row>
     <x:row r="61" ht="15.75" customHeight="1">
-      <x:c r="D61" s="22"/>
+      <x:c r="D61" s="13"/>
     </x:row>
     <x:row r="62" ht="15.75" customHeight="1">
-      <x:c r="D62" s="22"/>
+      <x:c r="D62" s="13"/>
     </x:row>
     <x:row r="63" ht="15.75" customHeight="1">
-      <x:c r="D63" s="22"/>
+      <x:c r="D63" s="13"/>
     </x:row>
     <x:row r="64" ht="15.75" customHeight="1">
-      <x:c r="D64" s="22"/>
+      <x:c r="D64" s="13"/>
     </x:row>
     <x:row r="65" ht="15.75" customHeight="1">
-      <x:c r="D65" s="22"/>
+      <x:c r="D65" s="13"/>
     </x:row>
     <x:row r="66" ht="15.75" customHeight="1">
-      <x:c r="D66" s="22"/>
+      <x:c r="D66" s="13"/>
     </x:row>
     <x:row r="67" ht="15.75" customHeight="1">
-      <x:c r="D67" s="22"/>
+      <x:c r="D67" s="13"/>
     </x:row>
     <x:row r="68" ht="15.75" customHeight="1">
-      <x:c r="D68" s="22"/>
+      <x:c r="D68" s="13"/>
     </x:row>
     <x:row r="69" ht="15.75" customHeight="1">
-      <x:c r="D69" s="22"/>
+      <x:c r="D69" s="13"/>
     </x:row>
     <x:row r="70" ht="15.75" customHeight="1">
-      <x:c r="D70" s="22"/>
+      <x:c r="D70" s="13"/>
     </x:row>
     <x:row r="71" ht="15.75" customHeight="1">
-      <x:c r="D71" s="22"/>
+      <x:c r="D71" s="13"/>
     </x:row>
     <x:row r="72" ht="15.75" customHeight="1">
-      <x:c r="D72" s="22"/>
+      <x:c r="D72" s="13"/>
     </x:row>
     <x:row r="73" ht="15.75" customHeight="1">
-      <x:c r="D73" s="22"/>
+      <x:c r="D73" s="13"/>
     </x:row>
     <x:row r="74" ht="15.75" customHeight="1">
-      <x:c r="D74" s="22"/>
+      <x:c r="D74" s="13"/>
     </x:row>
     <x:row r="75" ht="15.75" customHeight="1">
-      <x:c r="D75" s="22"/>
+      <x:c r="D75" s="13"/>
     </x:row>
     <x:row r="76" ht="15.75" customHeight="1">
-      <x:c r="D76" s="22"/>
+      <x:c r="D76" s="13"/>
     </x:row>
     <x:row r="77" ht="15.75" customHeight="1">
-      <x:c r="D77" s="22"/>
+      <x:c r="D77" s="13"/>
     </x:row>
     <x:row r="78" ht="15.75" customHeight="1">
-      <x:c r="D78" s="22"/>
+      <x:c r="D78" s="13"/>
     </x:row>
     <x:row r="79" ht="15.75" customHeight="1">
-      <x:c r="D79" s="22"/>
+      <x:c r="D79" s="13"/>
     </x:row>
     <x:row r="80" ht="15.75" customHeight="1">
-      <x:c r="D80" s="22"/>
+      <x:c r="D80" s="13"/>
     </x:row>
     <x:row r="81" ht="15.75" customHeight="1">
-      <x:c r="D81" s="22"/>
+      <x:c r="D81" s="13"/>
     </x:row>
     <x:row r="82" ht="15.75" customHeight="1">
-      <x:c r="D82" s="22"/>
+      <x:c r="D82" s="13"/>
     </x:row>
     <x:row r="83" ht="15.75" customHeight="1">
-      <x:c r="D83" s="22"/>
+      <x:c r="D83" s="13"/>
     </x:row>
     <x:row r="84" ht="15.75" customHeight="1">
-      <x:c r="D84" s="22"/>
+      <x:c r="D84" s="13"/>
     </x:row>
     <x:row r="85" ht="15.75" customHeight="1">
-      <x:c r="D85" s="22"/>
+      <x:c r="D85" s="13"/>
     </x:row>
     <x:row r="86" ht="15.75" customHeight="1">
-      <x:c r="D86" s="22"/>
+      <x:c r="D86" s="13"/>
     </x:row>
     <x:row r="87" ht="15.75" customHeight="1">
-      <x:c r="D87" s="22"/>
+      <x:c r="D87" s="13"/>
     </x:row>
     <x:row r="88" ht="15.75" customHeight="1">
-      <x:c r="D88" s="22"/>
+      <x:c r="D88" s="13"/>
     </x:row>
     <x:row r="89" ht="15.75" customHeight="1">
-      <x:c r="D89" s="22"/>
+      <x:c r="D89" s="13"/>
     </x:row>
     <x:row r="90" ht="15.75" customHeight="1">
-      <x:c r="D90" s="22"/>
+      <x:c r="D90" s="13"/>
     </x:row>
     <x:row r="91" ht="15.75" customHeight="1">
-      <x:c r="D91" s="22"/>
+      <x:c r="D91" s="13"/>
     </x:row>
     <x:row r="92" ht="15.75" customHeight="1">
-      <x:c r="D92" s="22"/>
+      <x:c r="D92" s="13"/>
     </x:row>
     <x:row r="93" ht="15.75" customHeight="1">
-      <x:c r="D93" s="22"/>
+      <x:c r="D93" s="13"/>
     </x:row>
     <x:row r="94" ht="15.75" customHeight="1">
-      <x:c r="D94" s="22"/>
+      <x:c r="D94" s="13"/>
     </x:row>
     <x:row r="95" ht="15.75" customHeight="1">
-      <x:c r="D95" s="22"/>
+      <x:c r="D95" s="13"/>
     </x:row>
     <x:row r="96" ht="15.75" customHeight="1">
-      <x:c r="D96" s="22"/>
+      <x:c r="D96" s="13"/>
     </x:row>
     <x:row r="97" ht="15.75" customHeight="1">
-      <x:c r="D97" s="22"/>
+      <x:c r="D97" s="13"/>
     </x:row>
     <x:row r="98" ht="15.75" customHeight="1">
-      <x:c r="D98" s="22"/>
+      <x:c r="D98" s="13"/>
     </x:row>
     <x:row r="99" ht="15.75" customHeight="1">
-      <x:c r="D99" s="22"/>
+      <x:c r="D99" s="13"/>
     </x:row>
     <x:row r="100" ht="15.75" customHeight="1">
-      <x:c r="D100" s="22"/>
+      <x:c r="D100" s="13"/>
     </x:row>
     <x:row r="101" ht="15.75" customHeight="1">
-      <x:c r="D101" s="22"/>
+      <x:c r="D101" s="13"/>
     </x:row>
     <x:row r="102" ht="15.75" customHeight="1">
-      <x:c r="D102" s="22"/>
+      <x:c r="D102" s="13"/>
     </x:row>
     <x:row r="103" ht="15.75" customHeight="1">
-      <x:c r="D103" s="22"/>
+      <x:c r="D103" s="13"/>
     </x:row>
     <x:row r="104" ht="15.75" customHeight="1">
-      <x:c r="D104" s="22"/>
+      <x:c r="D104" s="13"/>
     </x:row>
     <x:row r="105" ht="15.75" customHeight="1">
-      <x:c r="D105" s="22"/>
+      <x:c r="D105" s="13"/>
     </x:row>
     <x:row r="106" ht="15.75" customHeight="1">
-      <x:c r="D106" s="22"/>
+      <x:c r="D106" s="13"/>
     </x:row>
     <x:row r="107" ht="15.75" customHeight="1">
-      <x:c r="D107" s="22"/>
+      <x:c r="D107" s="13"/>
     </x:row>
     <x:row r="108" ht="15.75" customHeight="1">
-      <x:c r="D108" s="22"/>
+      <x:c r="D108" s="13"/>
     </x:row>
     <x:row r="109" ht="15.75" customHeight="1">
-      <x:c r="D109" s="22"/>
+      <x:c r="D109" s="13"/>
     </x:row>
     <x:row r="110" ht="15.75" customHeight="1">
-      <x:c r="D110" s="22"/>
+      <x:c r="D110" s="13"/>
     </x:row>
     <x:row r="111" ht="15.75" customHeight="1">
-      <x:c r="D111" s="22"/>
+      <x:c r="D111" s="13"/>
     </x:row>
     <x:row r="112" ht="15.75" customHeight="1">
-      <x:c r="D112" s="22"/>
+      <x:c r="D112" s="13"/>
     </x:row>
     <x:row r="113" ht="15.75" customHeight="1">
-      <x:c r="D113" s="22"/>
+      <x:c r="D113" s="13"/>
     </x:row>
     <x:row r="114" ht="15.75" customHeight="1">
-      <x:c r="D114" s="22"/>
+      <x:c r="D114" s="13"/>
     </x:row>
     <x:row r="115" ht="15.75" customHeight="1">
-      <x:c r="D115" s="22"/>
+      <x:c r="D115" s="13"/>
     </x:row>
     <x:row r="116" ht="15.75" customHeight="1">
-      <x:c r="D116" s="22"/>
+      <x:c r="D116" s="13"/>
     </x:row>
     <x:row r="117" ht="15.75" customHeight="1">
-      <x:c r="D117" s="22"/>
+      <x:c r="D117" s="13"/>
     </x:row>
     <x:row r="118" ht="15.75" customHeight="1">
-      <x:c r="D118" s="22"/>
+      <x:c r="D118" s="13"/>
     </x:row>
     <x:row r="119" ht="15.75" customHeight="1">
-      <x:c r="D119" s="22"/>
+      <x:c r="D119" s="13"/>
     </x:row>
     <x:row r="120" ht="15.75" customHeight="1">
-      <x:c r="D120" s="22"/>
+      <x:c r="D120" s="13"/>
     </x:row>
     <x:row r="121" ht="15.75" customHeight="1">
-      <x:c r="D121" s="22"/>
+      <x:c r="D121" s="13"/>
     </x:row>
     <x:row r="122" ht="15.75" customHeight="1">
-      <x:c r="D122" s="22"/>
+      <x:c r="D122" s="13"/>
     </x:row>
     <x:row r="123" ht="15.75" customHeight="1">
-      <x:c r="D123" s="22"/>
+      <x:c r="D123" s="13"/>
     </x:row>
     <x:row r="124" ht="15.75" customHeight="1">
-      <x:c r="D124" s="22"/>
+      <x:c r="D124" s="13"/>
     </x:row>
     <x:row r="125" ht="15.75" customHeight="1">
-      <x:c r="D125" s="22"/>
+      <x:c r="D125" s="13"/>
     </x:row>
     <x:row r="126" ht="15.75" customHeight="1">
-      <x:c r="D126" s="22"/>
+      <x:c r="D126" s="13"/>
     </x:row>
     <x:row r="127" ht="15.75" customHeight="1">
-      <x:c r="D127" s="22"/>
+      <x:c r="D127" s="13"/>
     </x:row>
     <x:row r="128" ht="15.75" customHeight="1">
-      <x:c r="D128" s="22"/>
+      <x:c r="D128" s="13"/>
     </x:row>
     <x:row r="129" ht="15.75" customHeight="1">
-      <x:c r="D129" s="22"/>
+      <x:c r="D129" s="13"/>
     </x:row>
     <x:row r="130" ht="15.75" customHeight="1">
-      <x:c r="D130" s="22"/>
+      <x:c r="D130" s="13"/>
     </x:row>
     <x:row r="131" ht="15.75" customHeight="1">
-      <x:c r="D131" s="22"/>
+      <x:c r="D131" s="13"/>
     </x:row>
     <x:row r="132" ht="15.75" customHeight="1">
-      <x:c r="D132" s="22"/>
+      <x:c r="D132" s="13"/>
     </x:row>
     <x:row r="133" ht="15.75" customHeight="1">
-      <x:c r="D133" s="22"/>
+      <x:c r="D133" s="13"/>
     </x:row>
     <x:row r="134" ht="15.75" customHeight="1">
-      <x:c r="D134" s="22"/>
+      <x:c r="D134" s="13"/>
     </x:row>
     <x:row r="135" ht="15.75" customHeight="1">
-      <x:c r="D135" s="22"/>
+      <x:c r="D135" s="13"/>
     </x:row>
     <x:row r="136" ht="15.75" customHeight="1">
-      <x:c r="D136" s="22"/>
+      <x:c r="D136" s="13"/>
     </x:row>
     <x:row r="137" ht="15.75" customHeight="1">
-      <x:c r="D137" s="22"/>
+      <x:c r="D137" s="13"/>
     </x:row>
     <x:row r="138" ht="15.75" customHeight="1">
-      <x:c r="D138" s="22"/>
+      <x:c r="D138" s="13"/>
     </x:row>
     <x:row r="139" ht="15.75" customHeight="1">
-      <x:c r="D139" s="22"/>
+      <x:c r="D139" s="13"/>
     </x:row>
     <x:row r="140" ht="15.75" customHeight="1">
-      <x:c r="D140" s="22"/>
+      <x:c r="D140" s="13"/>
     </x:row>
     <x:row r="141" ht="15.75" customHeight="1">
-      <x:c r="D141" s="22"/>
+      <x:c r="D141" s="13"/>
     </x:row>
     <x:row r="142" ht="15.75" customHeight="1">
-      <x:c r="D142" s="22"/>
+      <x:c r="D142" s="13"/>
     </x:row>
     <x:row r="143" ht="15.75" customHeight="1">
-      <x:c r="D143" s="22"/>
+      <x:c r="D143" s="13"/>
     </x:row>
     <x:row r="144" ht="15.75" customHeight="1">
-      <x:c r="D144" s="22"/>
+      <x:c r="D144" s="13"/>
     </x:row>
     <x:row r="145" ht="15.75" customHeight="1">
-      <x:c r="D145" s="22"/>
+      <x:c r="D145" s="13"/>
     </x:row>
     <x:row r="146" ht="15.75" customHeight="1">
-      <x:c r="D146" s="22"/>
+      <x:c r="D146" s="13"/>
     </x:row>
     <x:row r="147" ht="15.75" customHeight="1">
-      <x:c r="D147" s="22"/>
+      <x:c r="D147" s="13"/>
     </x:row>
     <x:row r="148" ht="15.75" customHeight="1">
-      <x:c r="D148" s="22"/>
+      <x:c r="D148" s="13"/>
     </x:row>
     <x:row r="149" ht="15.75" customHeight="1">
-      <x:c r="D149" s="22"/>
+      <x:c r="D149" s="13"/>
     </x:row>
     <x:row r="150" ht="15.75" customHeight="1">
-      <x:c r="D150" s="22"/>
+      <x:c r="D150" s="13"/>
     </x:row>
     <x:row r="151" ht="15.75" customHeight="1">
-      <x:c r="D151" s="22"/>
+      <x:c r="D151" s="13"/>
     </x:row>
     <x:row r="152" ht="15.75" customHeight="1">
-      <x:c r="D152" s="22"/>
+      <x:c r="D152" s="13"/>
     </x:row>
     <x:row r="153" ht="15.75" customHeight="1">
-      <x:c r="D153" s="22"/>
+      <x:c r="D153" s="13"/>
     </x:row>
     <x:row r="154" ht="15.75" customHeight="1">
-      <x:c r="D154" s="22"/>
+      <x:c r="D154" s="13"/>
     </x:row>
     <x:row r="155" ht="15.75" customHeight="1">
-      <x:c r="D155" s="22"/>
+      <x:c r="D155" s="13"/>
     </x:row>
     <x:row r="156" ht="15.75" customHeight="1">
-      <x:c r="D156" s="22"/>
+      <x:c r="D156" s="13"/>
     </x:row>
     <x:row r="157" ht="15.75" customHeight="1">
-      <x:c r="D157" s="22"/>
+      <x:c r="D157" s="13"/>
     </x:row>
     <x:row r="158" ht="15.75" customHeight="1">
-      <x:c r="D158" s="22"/>
+      <x:c r="D158" s="13"/>
     </x:row>
     <x:row r="159" ht="15.75" customHeight="1">
-      <x:c r="D159" s="22"/>
+      <x:c r="D159" s="13"/>
     </x:row>
     <x:row r="160" ht="15.75" customHeight="1">
-      <x:c r="D160" s="22"/>
+      <x:c r="D160" s="13"/>
     </x:row>
     <x:row r="161" ht="15.75" customHeight="1">
-      <x:c r="D161" s="22"/>
+      <x:c r="D161" s="13"/>
     </x:row>
     <x:row r="162" ht="15.75" customHeight="1">
-      <x:c r="D162" s="22"/>
+      <x:c r="D162" s="13"/>
     </x:row>
     <x:row r="163" ht="15.75" customHeight="1">
-      <x:c r="D163" s="22"/>
+      <x:c r="D163" s="13"/>
     </x:row>
     <x:row r="164" ht="15.75" customHeight="1">
-      <x:c r="D164" s="22"/>
+      <x:c r="D164" s="13"/>
     </x:row>
     <x:row r="165" ht="15.75" customHeight="1">
-      <x:c r="D165" s="22"/>
+      <x:c r="D165" s="13"/>
     </x:row>
     <x:row r="166" ht="15.75" customHeight="1">
-      <x:c r="D166" s="22"/>
+      <x:c r="D166" s="13"/>
     </x:row>
     <x:row r="167" ht="15.75" customHeight="1">
-      <x:c r="D167" s="22"/>
+      <x:c r="D167" s="13"/>
     </x:row>
     <x:row r="168" ht="15.75" customHeight="1">
-      <x:c r="D168" s="22"/>
+      <x:c r="D168" s="13"/>
     </x:row>
     <x:row r="169" ht="15.75" customHeight="1">
-      <x:c r="D169" s="22"/>
+      <x:c r="D169" s="13"/>
     </x:row>
     <x:row r="170" ht="15.75" customHeight="1">
-      <x:c r="D170" s="22"/>
+      <x:c r="D170" s="13"/>
     </x:row>
     <x:row r="171" ht="15.75" customHeight="1">
-      <x:c r="D171" s="22"/>
+      <x:c r="D171" s="13"/>
     </x:row>
     <x:row r="172" ht="15.75" customHeight="1">
-      <x:c r="D172" s="22"/>
+      <x:c r="D172" s="13"/>
     </x:row>
     <x:row r="173" ht="15.75" customHeight="1">
-      <x:c r="D173" s="22"/>
+      <x:c r="D173" s="13"/>
     </x:row>
     <x:row r="174" ht="15.75" customHeight="1">
-      <x:c r="D174" s="22"/>
+      <x:c r="D174" s="13"/>
     </x:row>
     <x:row r="175" ht="15.75" customHeight="1">
-      <x:c r="D175" s="22"/>
+      <x:c r="D175" s="13"/>
     </x:row>
     <x:row r="176" ht="15.75" customHeight="1">
-      <x:c r="D176" s="22"/>
+      <x:c r="D176" s="13"/>
     </x:row>
     <x:row r="177" ht="15.75" customHeight="1">
-      <x:c r="D177" s="22"/>
+      <x:c r="D177" s="13"/>
     </x:row>
     <x:row r="178" ht="15.75" customHeight="1">
-      <x:c r="D178" s="22"/>
+      <x:c r="D178" s="13"/>
     </x:row>
     <x:row r="179" ht="15.75" customHeight="1">
-      <x:c r="D179" s="22"/>
+      <x:c r="D179" s="13"/>
     </x:row>
     <x:row r="180" ht="15.75" customHeight="1">
-      <x:c r="D180" s="22"/>
+      <x:c r="D180" s="13"/>
     </x:row>
     <x:row r="181" ht="15.75" customHeight="1">
-      <x:c r="D181" s="22"/>
+      <x:c r="D181" s="13"/>
     </x:row>
     <x:row r="182" ht="15.75" customHeight="1">
-      <x:c r="D182" s="22"/>
+      <x:c r="D182" s="13"/>
     </x:row>
     <x:row r="183" ht="15.75" customHeight="1">
-      <x:c r="D183" s="22"/>
+      <x:c r="D183" s="13"/>
     </x:row>
     <x:row r="184" ht="15.75" customHeight="1">
-      <x:c r="D184" s="22"/>
+      <x:c r="D184" s="13"/>
     </x:row>
     <x:row r="185" ht="15.75" customHeight="1">
-      <x:c r="D185" s="22"/>
+      <x:c r="D185" s="13"/>
     </x:row>
     <x:row r="186" ht="15.75" customHeight="1">
-      <x:c r="D186" s="22"/>
+      <x:c r="D186" s="13"/>
     </x:row>
     <x:row r="187" ht="15.75" customHeight="1">
-      <x:c r="D187" s="22"/>
+      <x:c r="D187" s="13"/>
     </x:row>
     <x:row r="188" ht="15.75" customHeight="1">
-      <x:c r="D188" s="22"/>
+      <x:c r="D188" s="13"/>
     </x:row>
     <x:row r="189" ht="15.75" customHeight="1">
-      <x:c r="D189" s="22"/>
+      <x:c r="D189" s="13"/>
     </x:row>
     <x:row r="190" ht="15.75" customHeight="1">
-      <x:c r="D190" s="22"/>
+      <x:c r="D190" s="13"/>
     </x:row>
     <x:row r="191" ht="15.75" customHeight="1">
-      <x:c r="D191" s="22"/>
+      <x:c r="D191" s="13"/>
     </x:row>
     <x:row r="192" ht="15.75" customHeight="1">
-      <x:c r="D192" s="22"/>
+      <x:c r="D192" s="13"/>
     </x:row>
     <x:row r="193" ht="15.75" customHeight="1">
-      <x:c r="D193" s="22"/>
+      <x:c r="D193" s="13"/>
     </x:row>
     <x:row r="194" ht="15.75" customHeight="1">
-      <x:c r="D194" s="22"/>
+      <x:c r="D194" s="13"/>
     </x:row>
     <x:row r="195" ht="15.75" customHeight="1">
-      <x:c r="D195" s="22"/>
+      <x:c r="D195" s="13"/>
     </x:row>
     <x:row r="196" ht="15.75" customHeight="1">
-      <x:c r="D196" s="22"/>
+      <x:c r="D196" s="13"/>
     </x:row>
     <x:row r="197" ht="15.75" customHeight="1">
-      <x:c r="D197" s="22"/>
+      <x:c r="D197" s="13"/>
     </x:row>
     <x:row r="198" ht="15.75" customHeight="1">
-      <x:c r="D198" s="22"/>
+      <x:c r="D198" s="13"/>
     </x:row>
     <x:row r="199" ht="15.75" customHeight="1">
-      <x:c r="D199" s="22"/>
+      <x:c r="D199" s="13"/>
     </x:row>
     <x:row r="200" ht="15.75" customHeight="1">
-      <x:c r="D200" s="22"/>
+      <x:c r="D200" s="13"/>
     </x:row>
     <x:row r="201" ht="15.75" customHeight="1">
-      <x:c r="D201" s="22"/>
+      <x:c r="D201" s="13"/>
     </x:row>
     <x:row r="202" ht="15.75" customHeight="1">
-      <x:c r="D202" s="22"/>
+      <x:c r="D202" s="13"/>
     </x:row>
     <x:row r="203" ht="15.75" customHeight="1">
-      <x:c r="D203" s="22"/>
+      <x:c r="D203" s="13"/>
     </x:row>
     <x:row r="204" ht="15.75" customHeight="1">
-      <x:c r="D204" s="22"/>
+      <x:c r="D204" s="13"/>
     </x:row>
     <x:row r="205" ht="15.75" customHeight="1">
-      <x:c r="D205" s="22"/>
+      <x:c r="D205" s="13"/>
     </x:row>
     <x:row r="206" ht="15.75" customHeight="1">
-      <x:c r="D206" s="22"/>
+      <x:c r="D206" s="13"/>
     </x:row>
     <x:row r="207" ht="15.75" customHeight="1">
-      <x:c r="D207" s="22"/>
+      <x:c r="D207" s="13"/>
     </x:row>
     <x:row r="208" ht="15.75" customHeight="1">
-      <x:c r="D208" s="22"/>
+      <x:c r="D208" s="13"/>
     </x:row>
     <x:row r="209" ht="15.75" customHeight="1">
-      <x:c r="D209" s="22"/>
+      <x:c r="D209" s="13"/>
     </x:row>
     <x:row r="210" ht="15.75" customHeight="1">
-      <x:c r="D210" s="22"/>
+      <x:c r="D210" s="13"/>
     </x:row>
     <x:row r="211" ht="15.75" customHeight="1">
-      <x:c r="D211" s="22"/>
+      <x:c r="D211" s="13"/>
     </x:row>
     <x:row r="212" ht="15.75" customHeight="1">
-      <x:c r="D212" s="22"/>
+      <x:c r="D212" s="13"/>
     </x:row>
     <x:row r="213" ht="15.75" customHeight="1">
-      <x:c r="D213" s="22"/>
+      <x:c r="D213" s="13"/>
     </x:row>
     <x:row r="214" ht="15.75" customHeight="1">
-      <x:c r="D214" s="22"/>
+      <x:c r="D214" s="13"/>
     </x:row>
     <x:row r="215" ht="15.75" customHeight="1">
-      <x:c r="D215" s="22"/>
+      <x:c r="D215" s="13"/>
     </x:row>
     <x:row r="216" ht="15.75" customHeight="1">
-      <x:c r="D216" s="22"/>
+      <x:c r="D216" s="13"/>
     </x:row>
     <x:row r="217" ht="15.75" customHeight="1">
-      <x:c r="D217" s="22"/>
+      <x:c r="D217" s="13"/>
     </x:row>
     <x:row r="218" ht="15.75" customHeight="1">
-      <x:c r="D218" s="22"/>
+      <x:c r="D218" s="13"/>
     </x:row>
     <x:row r="219" ht="15.75" customHeight="1">
-      <x:c r="D219" s="22"/>
+      <x:c r="D219" s="13"/>
     </x:row>
     <x:row r="220" ht="15.75" customHeight="1">
-      <x:c r="D220" s="22"/>
+      <x:c r="D220" s="13"/>
     </x:row>
     <x:row r="221" ht="15.75" customHeight="1"/>
     <x:row r="222" ht="15.75" customHeight="1"/>
@@ -8942,7 +9484,7 @@
   <x:cols>
     <x:col min="1" max="3" width="12.630000114440918" customWidth="1"/>
     <x:col min="4" max="4" width="19" customWidth="1"/>
-    <x:col min="5" max="5" width="23.25" customWidth="1"/>
+    <x:col min="5" max="5" width="25.3799991607666" customWidth="1"/>
     <x:col min="6" max="6" width="12.630000114440918" customWidth="1"/>
     <x:col min="8" max="9" width="13" customWidth="1"/>
     <x:col min="10" max="10" width="20" customWidth="1"/>
@@ -8952,227 +9494,257 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
+      <x:c r="D3" s="3" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="13">
+      <x:c r="E3" s="16" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="16">
         <x:v>-21.25</x:v>
       </x:c>
-      <x:c r="I3" s="13">
+      <x:c r="I3" s="16">
         <x:v>-70.35</x:v>
       </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="K3" s="13" t="s">
+      <x:c r="J3" s="16" t="s">
         <x:v>111</x:v>
       </x:c>
+      <x:c r="K3" s="16" t="s">
+        <x:v>112</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="15.75" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
+      <x:c r="D4" s="3" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="F4" s="1" t="s">
+      <x:c r="E4" s="3" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="13">
+      <x:c r="F4" s="3" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G4" s="3"/>
+      <x:c r="H4" s="16">
         <x:v>-33.35</x:v>
       </x:c>
-      <x:c r="I4" s="13">
+      <x:c r="I4" s="16">
         <x:v>-71.85</x:v>
       </x:c>
-      <x:c r="J4" s="13" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="K4" s="13" t="s">
-        <x:v>115</x:v>
+      <x:c r="J4" s="16" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="s">
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15.75" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="D5" s="3" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
+      <x:c r="E5" s="3" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G5" s="1"/>
-      <x:c r="H5" s="13">
+      <x:c r="F5" s="3" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G5" s="3"/>
+      <x:c r="H5" s="16">
         <x:v>-36.0</x:v>
       </x:c>
-      <x:c r="I5" s="13">
+      <x:c r="I5" s="16">
         <x:v>-73.1</x:v>
       </x:c>
-      <x:c r="J5" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K5" s="13" t="s">
-        <x:v>119</x:v>
+      <x:c r="J5" s="16" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="s">
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15.75" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
         <x:v>4.0</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="D6" s="3" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E6" s="3" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F6" s="3" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="16">
+        <x:v>-23.35</x:v>
+      </x:c>
+      <x:c r="I6" s="16">
+        <x:v>-70.65</x:v>
+      </x:c>
+      <x:c r="J6" s="16" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K6" s="16" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15.75" customHeight="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
+        <x:v>5.0</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="16">
+        <x:v>-39.25</x:v>
+      </x:c>
+      <x:c r="I7" s="16">
+        <x:v>-73.4</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G6" s="1"/>
-      <x:c r="H6" s="13">
-        <x:v>-23.35</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>-70.65</x:v>
-      </x:c>
-      <x:c r="J6" s="13" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="s">
-        <x:v>123</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15.75" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
-        <x:v>5.0</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F7" s="21" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G7" s="1"/>
-      <x:c r="H7" s="13">
-        <x:v>-39.25</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>-73.4</x:v>
-      </x:c>
-      <x:c r="J7" s="13" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="s">
-        <x:v>126</x:v>
+      <x:c r="K7" s="16" t="s">
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="24" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F8" s="24" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="24" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E9" s="24" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F9" s="24" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="24" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F10" s="24" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="24" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E11" s="24" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="24" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F12" s="24" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -9181,7 +9753,11 @@
     <x:row r="17" ht="15.75" customHeight="1"/>
     <x:row r="18" ht="15.75" customHeight="1"/>
     <x:row r="19" ht="15.75" customHeight="1"/>
-    <x:row r="20" ht="15.75" customHeight="1"/>
+    <x:row r="20" ht="15.75" customHeight="1">
+      <x:c r="H20" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
     <x:row r="22" ht="15.75" customHeight="1"/>
     <x:row r="23" ht="15.75" customHeight="1"/>
@@ -10187,227 +10763,257 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G3" s="9"/>
-      <x:c r="H3" s="11">
+      <x:c r="D3" s="19" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G3" s="19"/>
+      <x:c r="H3" s="20">
         <x:v>-29.8</x:v>
       </x:c>
-      <x:c r="I3" s="11">
+      <x:c r="I3" s="20">
         <x:v>-71.5</x:v>
       </x:c>
-      <x:c r="J3" s="11" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="s">
-        <x:v>132</x:v>
+      <x:c r="J3" s="20" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="s">
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G4" s="9"/>
-      <x:c r="H4" s="11">
+      <x:c r="D4" s="19" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E4" s="19" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F4" s="19" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G4" s="19"/>
+      <x:c r="H4" s="20">
         <x:v>-33.2</x:v>
       </x:c>
-      <x:c r="I4" s="11">
+      <x:c r="I4" s="20">
         <x:v>-71.4</x:v>
       </x:c>
-      <x:c r="J4" s="11" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="s">
-        <x:v>136</x:v>
+      <x:c r="J4" s="20" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="s">
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="11">
+      <x:c r="D5" s="19" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G5" s="19"/>
+      <x:c r="H5" s="20">
         <x:v>-34.4</x:v>
       </x:c>
-      <x:c r="I5" s="11">
+      <x:c r="I5" s="20">
         <x:v>-72.3</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="K5" s="11" t="s">
-        <x:v>140</x:v>
+      <x:c r="J5" s="20" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="s">
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
         <x:v>4.0</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G6" s="9"/>
-      <x:c r="H6" s="11">
+      <x:c r="D6" s="19" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20">
         <x:v>-23.4</x:v>
       </x:c>
-      <x:c r="I6" s="11">
+      <x:c r="I6" s="20">
         <x:v>-70.2</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="s">
+      <x:c r="J6" s="20" t="s">
         <x:v>144</x:v>
       </x:c>
+      <x:c r="K6" s="20" t="s">
+        <x:v>157</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
         <x:v>5.0</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="11">
+      <x:c r="D7" s="19" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G7" s="19"/>
+      <x:c r="H7" s="20">
         <x:v>-41.6</x:v>
       </x:c>
-      <x:c r="I7" s="11">
+      <x:c r="I7" s="20">
         <x:v>-72.9</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="K7" s="11" t="s">
-        <x:v>148</x:v>
+      <x:c r="J7" s="20" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="s">
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="31" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="31" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E9" s="31" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F9" s="31" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="31" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E10" s="31" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F10" s="31" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="31" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E11" s="31" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F11" s="31" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="31" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E12" s="31" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F12" s="31" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -11422,227 +12028,227 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G3" s="9"/>
-      <x:c r="H3" s="11">
+      <x:c r="D3" s="19" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G3" s="19"/>
+      <x:c r="H3" s="20">
         <x:v>-22.91</x:v>
       </x:c>
-      <x:c r="I3" s="11">
+      <x:c r="I3" s="20">
         <x:v>-68.2</x:v>
       </x:c>
-      <x:c r="J3" s="11" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="s">
-        <x:v>154</x:v>
+      <x:c r="J3" s="20" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="s">
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G4" s="9"/>
-      <x:c r="H4" s="11">
+      <x:c r="D4" s="19" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="E4" s="19" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F4" s="19" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G4" s="19"/>
+      <x:c r="H4" s="20">
         <x:v>-27.45</x:v>
       </x:c>
-      <x:c r="I4" s="11">
+      <x:c r="I4" s="20">
         <x:v>-71.4</x:v>
       </x:c>
-      <x:c r="J4" s="11" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="s">
-        <x:v>159</x:v>
+      <x:c r="J4" s="20" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="s">
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="11">
+      <x:c r="D5" s="19" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G5" s="19"/>
+      <x:c r="H5" s="20">
         <x:v>-29.9</x:v>
       </x:c>
-      <x:c r="I5" s="11">
+      <x:c r="I5" s="20">
         <x:v>-71.6</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="K5" s="11" t="s">
-        <x:v>163</x:v>
+      <x:c r="J5" s="20" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="s">
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
         <x:v>4.0</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G6" s="9"/>
-      <x:c r="H6" s="11">
+      <x:c r="D6" s="19" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20">
         <x:v>-20.48</x:v>
       </x:c>
-      <x:c r="I6" s="11">
+      <x:c r="I6" s="20">
         <x:v>-69.33</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="s">
-        <x:v>167</x:v>
+      <x:c r="J6" s="20" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="s">
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
         <x:v>5.0</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="11">
+      <x:c r="D7" s="19" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G7" s="19"/>
+      <x:c r="H7" s="20">
         <x:v>-33.05</x:v>
       </x:c>
-      <x:c r="I7" s="11">
+      <x:c r="I7" s="20">
         <x:v>-72.0</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="K7" s="11" t="s">
-        <x:v>171</x:v>
+      <x:c r="J7" s="20" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="s">
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="3"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -12657,227 +13263,227 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
-      <x:c r="B3" s="7" t="str">
-        <x:v>MISTRAL AI</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="str">
-        <x:v>22/09/2026 00:00 – 24/09/2026 00:00 (48 h)</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="str">
-        <x:v>Valparaíso</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="str">
-        <x:v>M5.0–6.0</x:v>
-      </x:c>
-      <x:c r="G3" s="9"/>
-      <x:c r="H3" s="11" t="n">
+      <x:c r="B3" s="7" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="D3" s="19" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G3" s="19"/>
+      <x:c r="H3" s="20">
         <x:v>-33.047</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="n">
+      <x:c r="I3" s="20">
         <x:v>-71.613</x:v>
       </x:c>
-      <x:c r="J3" s="11" t="str">
-        <x:v>Zona costera de referencia</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="str">
-        <x:v>Valparaíso, Región de Valparaíso. Hipótesis basada en actividad histórica en la zona central; ventana de 48 horas.</x:v>
+      <x:c r="J3" s="20" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="s">
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>23/09/2026 06:00 – 26/09/2026 06:00 (72 h)</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="str">
-        <x:v>Concepción</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="str">
-        <x:v>M4.8–5.8</x:v>
-      </x:c>
-      <x:c r="G4" s="9"/>
-      <x:c r="H4" s="11" t="n">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="D4" s="19" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="E4" s="19" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F4" s="19" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G4" s="19"/>
+      <x:c r="H4" s="20">
         <x:v>-36.827</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="n">
+      <x:c r="I4" s="20">
         <x:v>-73.05</x:v>
       </x:c>
-      <x:c r="J4" s="11" t="str">
-        <x:v>Zona costera de referencia</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="str">
-        <x:v>Concepción, Región del Biobío. Mistral menciona la falla de Pichilemu como supuesto; no se verifica relación geográfica con Concepción.</x:v>
+      <x:c r="J4" s="20" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="s">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="str">
-        <x:v>24/09/2026 12:00 – 27/09/2026 00:00 (60 h)</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="str">
-        <x:v>Iquique</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="str">
-        <x:v>M5.5–6.5</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="11" t="n">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
+        <x:v>3.0</x:v>
+      </x:c>
+      <x:c r="D5" s="19" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G5" s="19"/>
+      <x:c r="H5" s="20">
         <x:v>-20.202</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="n">
+      <x:c r="I5" s="20">
         <x:v>-70.135</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="str">
-        <x:v>Zona costera de referencia</x:v>
-      </x:c>
-      <x:c r="K5" s="11" t="str">
-        <x:v>Iquique, Región de Tarapacá. Estimación experimental para el Norte Grande; ventana de 60 horas.</x:v>
+      <x:c r="J5" s="20" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="s">
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="str">
-        <x:v>25/09/2026 18:00 – 28/09/2026 00:00 (54 h)</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="str">
-        <x:v>Puerto Montt</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="str">
-        <x:v>M4.5–5.5</x:v>
-      </x:c>
-      <x:c r="G6" s="9"/>
-      <x:c r="H6" s="11" t="n">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
+        <x:v>4.0</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20">
         <x:v>-41.47</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="n">
+      <x:c r="I6" s="20">
         <x:v>-72.942</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="str">
-        <x:v>Zona sur de referencia</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="str">
-        <x:v>Puerto Montt, Región de Los Lagos. Mistral señala zona de subducción sur; ventana de 54 horas.</x:v>
+      <x:c r="J6" s="20" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="s">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="str">
-        <x:v>26/09/2026 03:00 – 28/09/2026 23:00 (68 h; fuente indica 70 h)</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="str">
-        <x:v>Copiapó</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="str">
-        <x:v>M5.2–6.2</x:v>
-      </x:c>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="11" t="n">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
+        <x:v>5.0</x:v>
+      </x:c>
+      <x:c r="D7" s="19" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G7" s="19"/>
+      <x:c r="H7" s="20">
         <x:v>-27.366</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="n">
+      <x:c r="I7" s="20">
         <x:v>-70.33</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="str">
-        <x:v>Zona interior de referencia</x:v>
-      </x:c>
-      <x:c r="K7" s="11" t="str">
-        <x:v>Copiapó, Región de Atacama. Hipótesis de actividad en el desierto de Atacama. Las horas indicadas suman 68 h, aunque Mistral escribió 70 h.</x:v>
+      <x:c r="J7" s="20" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="s">
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="3"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -13892,227 +14498,227 @@
     <x:row r="1" ht="15.75" customHeight="1"/>
     <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="D2" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G3" s="9"/>
-      <x:c r="H3" s="11">
+      <x:c r="D3" s="19" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G3" s="19"/>
+      <x:c r="H3" s="20">
         <x:v>-20.5</x:v>
       </x:c>
-      <x:c r="I3" s="11">
+      <x:c r="I3" s="20">
         <x:v>-69.3</x:v>
       </x:c>
-      <x:c r="J3" s="11" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="s">
-        <x:v>177</x:v>
+      <x:c r="J3" s="20" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="s">
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
-      <x:c r="B4" s="14"/>
-      <x:c r="C4" s="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
         <x:v>2.0</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G4" s="9"/>
-      <x:c r="H4" s="11">
+      <x:c r="D4" s="19" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="E4" s="19" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F4" s="19" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G4" s="19"/>
+      <x:c r="H4" s="20">
         <x:v>-23.8</x:v>
       </x:c>
-      <x:c r="I4" s="11">
+      <x:c r="I4" s="20">
         <x:v>-68.1</x:v>
       </x:c>
-      <x:c r="J4" s="11" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="s">
-        <x:v>182</x:v>
+      <x:c r="J4" s="20" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="s">
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="G5" s="9"/>
-      <x:c r="H5" s="11">
+      <x:c r="D5" s="19" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G5" s="19"/>
+      <x:c r="H5" s="20">
         <x:v>-32.9</x:v>
       </x:c>
-      <x:c r="I5" s="11">
+      <x:c r="I5" s="20">
         <x:v>-71.8</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="K5" s="11" t="s">
-        <x:v>187</x:v>
+      <x:c r="J5" s="20" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="s">
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
         <x:v>4.0</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="G6" s="9"/>
-      <x:c r="H6" s="11">
+      <x:c r="D6" s="19" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20">
         <x:v>-27.1</x:v>
       </x:c>
-      <x:c r="I6" s="11">
+      <x:c r="I6" s="20">
         <x:v>-70.9</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="s">
-        <x:v>192</x:v>
+      <x:c r="J6" s="20" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="s">
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
         <x:v>5.0</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="11">
+      <x:c r="D7" s="32" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G7" s="19"/>
+      <x:c r="H7" s="20">
         <x:v>-37.2</x:v>
       </x:c>
-      <x:c r="I7" s="11">
+      <x:c r="I7" s="20">
         <x:v>-73.6</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="K7" s="11" t="s">
-        <x:v>197</x:v>
+      <x:c r="J7" s="20" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="s">
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="1">
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="3">
         <x:v>6.0</x:v>
       </x:c>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="1">
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3">
         <x:v>7.0</x:v>
       </x:c>
-      <x:c r="D9" s="1"/>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="1">
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3">
         <x:v>8.0</x:v>
       </x:c>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="1">
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3">
         <x:v>9.0</x:v>
       </x:c>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
+      <x:c r="D11" s="3"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="1">
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3">
         <x:v>10.0</x:v>
       </x:c>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>

--- a/Proyecto_Tabla_de_datos_con_coordenadas.xlsx
+++ b/Proyecto_Tabla_de_datos_con_coordenadas.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRUEBA" sheetId="1" r:id="Rb7724335ba324e57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GROK" sheetId="2" r:id="R142ebc71630a4571"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEEPSEEK" sheetId="3" r:id="Rf7ae5cf6407b46ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHATGPT" sheetId="4" r:id="R5dcbe6e2d773434a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLAUDE" sheetId="5" r:id="Re2c168eb8e9d4e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERPLEXITY" sheetId="6" r:id="R90660a673da64359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META AI" sheetId="7" r:id="Rbb30deb1a6e547e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MISTRAL AI" sheetId="8" r:id="Rc501871970bb4d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMINI" sheetId="9" r:id="R137adff7c05243a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COPILOT" sheetId="10" r:id="Rc0c5b56266c44d88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QWEN" sheetId="11" r:id="R05c40cd4f3f34a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 1" sheetId="12" r:id="R16e2812486744b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRUEBA" sheetId="1" r:id="R20820bb927e84737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GROK" sheetId="2" r:id="Ra604cb9aae0f4f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEEPSEEK" sheetId="3" r:id="R8d6f50da59bc4df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHATGPT" sheetId="4" r:id="Rffd0cd7a6a3e40c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLAUDE" sheetId="5" r:id="Rb993799201af4c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERPLEXITY" sheetId="6" r:id="Rea1a64fb8f1649d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META AI" sheetId="7" r:id="R2c1918abfaa34991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MISTRAL AI" sheetId="8" r:id="Re4031761638b4964"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMINI" sheetId="9" r:id="R49a186e875db4bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COPILOT" sheetId="10" r:id="Rce3fe347da0d42be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QWEN" sheetId="11" r:id="Rc691b876828d4678"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 1" sheetId="12" r:id="Ra1c358244066481e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,6 +345,66 @@
     <x:t xml:space="preserve">M6,0–7,0</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">CHATGPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10 - 13/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa de Tarapacá - Antofagasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M4,0 - 5,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Franja costera amplia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado costa Tarapacá–Antofagasta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Costa de Atacama - Coquimbo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3,5 - 4,8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado costa Atacama–Coquimbo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Valparaíso - O´Higgins</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3,5 - 4,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Franja regional amplia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado Valparaíso–O'Higgins</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Maule - Araucanía</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3,5–4,7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado Maule–Araucanía</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Norte/centro de Chile, Antofagasta - Coquimbo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">M3,5–5,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Macro-zona</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Centro aproximado Antofagasta–Coquimbo</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">CLAUDE</x:t>
   </x:si>
   <x:si>
@@ -381,9 +441,6 @@
     <x:t xml:space="preserve">M3.8</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Franja costera amplia</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Centro aproximado costa Maule–Biobío</x:t>
   </x:si>
   <x:si>
@@ -769,9 +826,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">4.0/5.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Macro-zona</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Centro aproximado entre ambas regiones</x:t>
@@ -886,13 +940,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy hh:mm"/>
-    <x:numFmt numFmtId="201" formatCode="0.00"/>
-    <x:numFmt numFmtId="202" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF000000"/>
@@ -948,14 +999,8 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FF111111"/>
-      <x:name val="Arial"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -970,11 +1015,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1033,7 +1073,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="94">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -1112,164 +1152,6 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2743,19 +2625,19 @@
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>246</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E3" s="33" t="s">
-        <x:v>248</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F3" s="33" t="s">
-        <x:v>249</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G3" s="3"/>
       <x:c r="H3" s="16">
@@ -2765,10 +2647,10 @@
         <x:v>-70.5</x:v>
       </x:c>
       <x:c r="J3" s="16" t="s">
-        <x:v>250</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K3" s="16" t="s">
-        <x:v>251</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15.75" customHeight="1">
@@ -2777,13 +2659,13 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E4" s="33" t="s">
-        <x:v>252</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="F4" s="33" t="s">
-        <x:v>253</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G4" s="3"/>
       <x:c r="H4" s="16">
@@ -2793,10 +2675,10 @@
         <x:v>-72.6</x:v>
       </x:c>
       <x:c r="J4" s="16" t="s">
-        <x:v>250</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K4" s="16" t="s">
-        <x:v>254</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15.75" customHeight="1">
@@ -2805,13 +2687,13 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E5" s="33" t="s">
-        <x:v>255</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="F5" s="33" t="s">
-        <x:v>256</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G5" s="3"/>
       <x:c r="H5" s="16">
@@ -2824,7 +2706,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="K5" s="16" t="s">
-        <x:v>257</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15.75" customHeight="1">
@@ -2833,13 +2715,13 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E6" s="33" t="s">
-        <x:v>258</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="F6" s="33" t="s">
-        <x:v>259</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G6" s="3"/>
       <x:c r="H6" s="16">
@@ -2849,10 +2731,10 @@
         <x:v>-71.0</x:v>
       </x:c>
       <x:c r="J6" s="16" t="s">
-        <x:v>250</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K6" s="16" t="s">
-        <x:v>260</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15.75" customHeight="1">
@@ -2861,13 +2743,13 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E7" s="33" t="s">
-        <x:v>261</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F7" s="33" t="s">
-        <x:v>259</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G7" s="3"/>
       <x:c r="H7" s="16">
@@ -2877,10 +2759,10 @@
         <x:v>-69.8</x:v>
       </x:c>
       <x:c r="J7" s="16" t="s">
-        <x:v>250</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K7" s="16" t="s">
-        <x:v>262</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
@@ -3978,19 +3860,19 @@
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>263</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="D3" s="19" t="s">
-        <x:v>264</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>265</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>266</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20">
@@ -4000,10 +3882,10 @@
         <x:v>-68.5</x:v>
       </x:c>
       <x:c r="J3" s="20" t="s">
-        <x:v>267</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="K3" s="20" t="s">
-        <x:v>268</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
@@ -4012,10 +3894,10 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="D4" s="19" t="s">
-        <x:v>269</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E4" s="19" t="s">
-        <x:v>270</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F4" s="19" t="s">
         <x:v>84</x:v>
@@ -4028,10 +3910,10 @@
         <x:v>-70.8</x:v>
       </x:c>
       <x:c r="J4" s="20" t="s">
-        <x:v>271</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="K4" s="20" t="s">
-        <x:v>272</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
@@ -4040,13 +3922,13 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="D5" s="19" t="s">
-        <x:v>273</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E5" s="19" t="s">
-        <x:v>274</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F5" s="19" t="s">
-        <x:v>275</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G5" s="19"/>
       <x:c r="H5" s="20">
@@ -4056,10 +3938,10 @@
         <x:v>-70.7</x:v>
       </x:c>
       <x:c r="J5" s="20" t="s">
-        <x:v>276</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="K5" s="20" t="s">
-        <x:v>277</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -4068,13 +3950,13 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="D6" s="19" t="s">
-        <x:v>278</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="E6" s="19" t="s">
-        <x:v>279</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="F6" s="19" t="s">
-        <x:v>280</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="G6" s="19"/>
       <x:c r="H6" s="20">
@@ -4084,10 +3966,10 @@
         <x:v>-72.5</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>281</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="K6" s="20" t="s">
-        <x:v>282</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -4096,13 +3978,13 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="D7" s="19" t="s">
-        <x:v>283</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E7" s="19" t="s">
-        <x:v>284</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F7" s="19" t="s">
-        <x:v>275</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G7" s="19"/>
       <x:c r="H7" s="20">
@@ -4112,10 +3994,10 @@
         <x:v>-74.5</x:v>
       </x:c>
       <x:c r="J7" s="20" t="s">
-        <x:v>285</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="K7" s="20" t="s">
-        <x:v>286</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
@@ -5375,6 +5257,18 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="G8" s="2"/>
+      <x:c r="H8" t="n">
+        <x:v>-22.45</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>-68.85</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Zona interior</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>Referencia aproximada Calama–NE de Antofagasta</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
       <x:c r="B9" s="17"/>
@@ -5391,6 +5285,18 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="G9" s="2"/>
+      <x:c r="H9" t="n">
+        <x:v>-20.75</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>-69.15</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Zona interior/altiplánica</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>Centro aproximado Camiña–Collahuasi</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
       <x:c r="B10" s="17"/>
@@ -5407,6 +5313,18 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="G10" s="2"/>
+      <x:c r="H10" t="n">
+        <x:v>-33.75</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>-72.05</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Zona offshore costera</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>Referencia frente a San Antonio–Navidad</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
       <x:c r="B11" s="17"/>
@@ -5423,6 +5341,18 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="G11" s="2"/>
+      <x:c r="H11" t="n">
+        <x:v>-29.5</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>-71.25</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Zona regional interior-costera</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>Referencia aproximada La Higuera, Coquimbo</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
       <x:c r="B12" s="29"/>
@@ -5439,6 +5369,18 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="G12" s="2"/>
+      <x:c r="H12" t="n">
+        <x:v>-21.8</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>-68.45</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Zona interior/altiplánica</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>Referencia aproximada NE de San Pedro de Atacama–Ollagüe</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1">
       <x:c r="B13" s="27"/>
@@ -6647,6 +6589,18 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G8" s="3"/>
+      <x:c r="H8" t="n">
+        <x:v>-29</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>-71.1</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Macro-zona costera</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>Centro aproximado Atacama–Coquimbo</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
       <x:c r="B9" s="17"/>
@@ -6663,6 +6617,18 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="G9" s="3"/>
+      <x:c r="H9" t="n">
+        <x:v>-21.8</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>-69.9</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Macro-zona norte</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>Centro aproximado Arica–Iquique–Antofagasta</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
       <x:c r="B10" s="17"/>
@@ -6679,6 +6645,18 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="G10" s="3"/>
+      <x:c r="H10" t="n">
+        <x:v>-34.8</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>-72.1</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Macro-zona centro costera</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>Centro aproximado Valparaíso–Maule</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
       <x:c r="B11" s="17"/>
@@ -6695,6 +6673,18 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="G11" s="3"/>
+      <x:c r="H11" t="n">
+        <x:v>-39.5</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>-73</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Macro-zona centro-sur</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>Centro aproximado Biobío–Los Lagos</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
       <x:c r="B12" s="29"/>
@@ -6711,6 +6701,18 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="G12" s="3"/>
+      <x:c r="H12" t="n">
+        <x:v>-27.4</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>-70.5</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Región amplia</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>Referencia aproximada Región de Atacama</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -7713,36 +7715,26 @@
   <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="3" width="12.630000114440918" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.880000114440918" customWidth="1"/>
+    <x:col min="5" max="5" width="40.5" customWidth="1"/>
+    <x:col min="6" max="6" width="9.75" customWidth="1"/>
     <x:col min="8" max="9" width="13" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="21" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="21" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" customWidth="1"/>
+    <x:col min="11" max="11" width="38" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15.75" customHeight="1">
       <x:c r="D1" s="13"/>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
+    <x:row r="2" ht="15.75" customHeight="1">
       <x:c r="B2" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D2" s="18" t="str">
-        <x:v>Dia/Mes</x:v>
+      <x:c r="D2" s="18" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
         <x:v>40</x:v>
@@ -7753,318 +7745,307 @@
       <x:c r="G2" s="3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H2" s="68" t="s">
+      <x:c r="H2" s="5" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I2" s="68" t="s">
+      <x:c r="I2" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J2" s="68" t="s">
+      <x:c r="J2" s="5" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K2" s="68" t="s">
+      <x:c r="K2" s="5" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L2" s="68" t="str">
-        <x:v>Fecha estimada</x:v>
-      </x:c>
-      <x:c r="M2" s="68" t="str">
-        <x:v>Hora estimada</x:v>
-      </x:c>
-      <x:c r="N2" s="68" t="str">
-        <x:v>Inicio ventana</x:v>
-      </x:c>
-      <x:c r="O2" s="68" t="str">
-        <x:v>Fin ventana</x:v>
-      </x:c>
-      <x:c r="P2" s="68" t="str">
-        <x:v>Confianza</x:v>
-      </x:c>
-      <x:c r="Q2" s="68" t="str">
-        <x:v>Rango M</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="34" customHeight="1">
-      <x:c r="B3" s="7" t="str">
+    </x:row>
+    <x:row r="3" ht="15.75" customHeight="1">
+      <x:c r="B3" s="7" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E3" s="18" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F3" s="18" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="16">
+        <x:v>-21.9</x:v>
+      </x:c>
+      <x:c r="I3" s="16">
+        <x:v>-70.35</x:v>
+      </x:c>
+      <x:c r="J3" s="16" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K3" s="16" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15.75" customHeight="1">
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="3">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E4" s="21" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G4" s="3"/>
+      <x:c r="H4" s="16">
+        <x:v>-28.9</x:v>
+      </x:c>
+      <x:c r="I4" s="16">
+        <x:v>-71.45</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15.75" customHeight="1">
+      <x:c r="B5" s="17"/>
+      <x:c r="C5" s="3">
+        <x:v>3.0</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E5" s="18" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F5" s="18" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G5" s="3"/>
+      <x:c r="H5" s="16">
+        <x:v>-33.8</x:v>
+      </x:c>
+      <x:c r="I5" s="16">
+        <x:v>-71.2</x:v>
+      </x:c>
+      <x:c r="J5" s="16" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15.75" customHeight="1">
+      <x:c r="B6" s="17"/>
+      <x:c r="C6" s="3">
+        <x:v>4.0</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F6" s="18" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="16">
+        <x:v>-37.0</x:v>
+      </x:c>
+      <x:c r="I6" s="16">
+        <x:v>-72.2</x:v>
+      </x:c>
+      <x:c r="J6" s="16" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K6" s="16" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15.75" customHeight="1">
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="3">
+        <x:v>5.0</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F7" s="18" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="16">
+        <x:v>-27.0</x:v>
+      </x:c>
+      <x:c r="I7" s="16">
+        <x:v>-70.6</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K7" s="16" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15.75" customHeight="1">
+      <x:c r="A8"/>
+      <x:c r="B8" s="17" t="str">
         <x:v>CHATGPT</x:v>
       </x:c>
-      <x:c r="C3" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="85" t="str">
-        <x:v>02/10/2026 - 04/10/2026</x:v>
-      </x:c>
-      <x:c r="E3" s="92" t="str">
+      <x:c r="C8" s="3" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>02 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
         <x:v>Costa de Antofagasta, entre Mejillones y Taltal</x:v>
       </x:c>
-      <x:c r="F3" s="85" t="str">
-        <x:v>M4,0</x:v>
-      </x:c>
-      <x:c r="G3" s="84"/>
-      <x:c r="H3" s="86" t="n">
-        <x:v>-24.25</x:v>
-      </x:c>
-      <x:c r="I3" s="86" t="n">
-        <x:v>-70.75</x:v>
-      </x:c>
-      <x:c r="J3" s="93" t="str">
+      <x:c r="F8" s="3" t="str">
+        <x:v>M3,5 - 4,5</x:v>
+      </x:c>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" t="n">
+        <x:v>-23.5</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>-70.6</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
         <x:v>Franja costera</x:v>
       </x:c>
-      <x:c r="K3" s="93" t="str">
-        <x:v>Centro aproximado de la costa de Antofagasta, entre Mejillones y Taltal</x:v>
-      </x:c>
-      <x:c r="L3" s="88" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="M3" s="89" t="str">
-        <x:v>08:30</x:v>
-      </x:c>
-      <x:c r="N3" s="90" t="n">
-        <x:v>46297.833333333336</x:v>
-      </x:c>
-      <x:c r="O3" s="90" t="n">
-        <x:v>46299.833333333336</x:v>
-      </x:c>
-      <x:c r="P3" s="91" t="n">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="Q3" s="89" t="str">
-        <x:v>M3,5–4,5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="34" customHeight="1">
-      <x:c r="B4" s="17"/>
-      <x:c r="C4" s="84" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="85" t="str">
-        <x:v>02/10/2026 - 04/10/2026</x:v>
-      </x:c>
-      <x:c r="E4" s="82" t="str">
-        <x:v>Región de Tarapacá, zona Iquique–Pica</x:v>
-      </x:c>
-      <x:c r="F4" s="87" t="str">
-        <x:v>M3,7</x:v>
-      </x:c>
-      <x:c r="G4" s="84"/>
-      <x:c r="H4" s="86" t="n">
-        <x:v>-20.35</x:v>
-      </x:c>
-      <x:c r="I4" s="86" t="n">
+      <x:c r="K8" t="str">
+        <x:v>Referencia costera entre Mejillones y Taltal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15.75" customHeight="1">
+      <x:c r="A9"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="3" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>02 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>Región de Tarapacá, zona de Iquique - Pica</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>M3,3 - 4,1</x:v>
+      </x:c>
+      <x:c r="G9" s="3"/>
+      <x:c r="H9" t="n">
+        <x:v>-20.3</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
         <x:v>-69.8</x:v>
       </x:c>
-      <x:c r="J4" s="93" t="str">
-        <x:v>Corredor costa–interior</x:v>
-      </x:c>
-      <x:c r="K4" s="93" t="str">
-        <x:v>Punto de referencia aproximado entre Iquique y Pica, Región de Tarapacá</x:v>
-      </x:c>
-      <x:c r="L4" s="88" t="n">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="M4" s="89" t="str">
-        <x:v>22:10</x:v>
-      </x:c>
-      <x:c r="N4" s="90" t="n">
-        <x:v>46297.416666666664</x:v>
-      </x:c>
-      <x:c r="O4" s="90" t="n">
-        <x:v>46299.416666666664</x:v>
-      </x:c>
-      <x:c r="P4" s="91" t="n">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="Q4" s="89" t="str">
-        <x:v>M3,2–4,2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="B5" s="17"/>
-      <x:c r="C5" s="84" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="85" t="str">
-        <x:v>02/10/2026 - 04/10/2026</x:v>
-      </x:c>
-      <x:c r="E5" s="92" t="str">
-        <x:v>Costa de Coquimbo, entre La Serena y Los Vilos</x:v>
-      </x:c>
-      <x:c r="F5" s="85" t="str">
-        <x:v>M4,2</x:v>
-      </x:c>
-      <x:c r="G5" s="84"/>
-      <x:c r="H5" s="86" t="n">
-        <x:v>-30.9</x:v>
-      </x:c>
-      <x:c r="I5" s="86" t="n">
-        <x:v>-71.5</x:v>
-      </x:c>
-      <x:c r="J5" s="93" t="str">
+      <x:c r="J9" t="str">
+        <x:v>Costa e interior</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>Referencia aproximada del corredor Iquique–Pica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15.75" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>02 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>Región de Coquimbo, costa entre La Serena y Los Vilos</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>M3,8 - 4,6</x:v>
+      </x:c>
+      <x:c r="G10" s="3"/>
+      <x:c r="H10" t="n">
+        <x:v>-31</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>-71.6</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
         <x:v>Franja costera</x:v>
       </x:c>
-      <x:c r="K5" s="93" t="str">
-        <x:v>Centro aproximado de la costa entre La Serena y Los Vilos</x:v>
-      </x:c>
-      <x:c r="L5" s="88" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="M5" s="89" t="str">
-        <x:v>15:40</x:v>
-      </x:c>
-      <x:c r="N5" s="90" t="n">
-        <x:v>46297.625</x:v>
-      </x:c>
-      <x:c r="O5" s="90" t="n">
-        <x:v>46299.958333333336</x:v>
-      </x:c>
-      <x:c r="P5" s="91" t="n">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="Q5" s="89" t="str">
-        <x:v>M3,7–4,7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="34" customHeight="1">
-      <x:c r="B6" s="17"/>
-      <x:c r="C6" s="84" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="85" t="str">
-        <x:v>03/10/2026 - 04/10/2026</x:v>
-      </x:c>
-      <x:c r="E6" s="92" t="str">
-        <x:v>Región de Atacama, zona Copiapó–Caldera</x:v>
-      </x:c>
-      <x:c r="F6" s="85" t="str">
-        <x:v>M3,8</x:v>
-      </x:c>
-      <x:c r="G6" s="84"/>
-      <x:c r="H6" s="86" t="n">
-        <x:v>-27.22</x:v>
-      </x:c>
-      <x:c r="I6" s="86" t="n">
-        <x:v>-70.58</x:v>
-      </x:c>
-      <x:c r="J6" s="93" t="str">
-        <x:v>Corredor costa–interior</x:v>
-      </x:c>
-      <x:c r="K6" s="93" t="str">
-        <x:v>Punto medio aproximado entre Copiapó y Caldera, Región de Atacama</x:v>
-      </x:c>
-      <x:c r="L6" s="88" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="M6" s="89" t="str">
-        <x:v>01:20</x:v>
-      </x:c>
-      <x:c r="N6" s="90" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="O6" s="90" t="n">
-        <x:v>46299.99930555555</x:v>
-      </x:c>
-      <x:c r="P6" s="91" t="n">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="Q6" s="89" t="str">
-        <x:v>M3,3–4,3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="34" customHeight="1">
-      <x:c r="B7" s="17"/>
-      <x:c r="C7" s="84" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="85" t="str">
-        <x:v>02/10/2026 - 03/10/2026</x:v>
-      </x:c>
-      <x:c r="E7" s="92" t="str">
-        <x:v>Región de Valparaíso, frente a San Antonio</x:v>
-      </x:c>
-      <x:c r="F7" s="85" t="str">
-        <x:v>M3,6</x:v>
-      </x:c>
-      <x:c r="G7" s="84"/>
-      <x:c r="H7" s="86" t="n">
+      <x:c r="K10" t="str">
+        <x:v>Referencia aproximada de la costa de Coquimbo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15.75" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="str">
+        <x:v>03 - 04/10/2026</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>Región de Atacama, zona de Copiapó - Caldera</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>M3,4 - 4,2</x:v>
+      </x:c>
+      <x:c r="G11" s="3"/>
+      <x:c r="H11" t="n">
+        <x:v>-27.1</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>-70.6</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Costa e interior</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>Referencia aproximada del corredor Copiapó–Caldera</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15.75" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" s="29"/>
+      <x:c r="C12" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>02 - 03/10/2026</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>Región de Valparaíso, zona costera frente a San Antonio</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>M3,2 - 4,0</x:v>
+      </x:c>
+      <x:c r="G12" s="3"/>
+      <x:c r="H12" t="n">
         <x:v>-33.6</x:v>
       </x:c>
-      <x:c r="I7" s="86" t="n">
-        <x:v>-72</x:v>
-      </x:c>
-      <x:c r="J7" s="93" t="str">
-        <x:v>Zona costera / mar adentro</x:v>
-      </x:c>
-      <x:c r="K7" s="93" t="str">
-        <x:v>Referencia aproximada mar adentro frente a San Antonio</x:v>
-      </x:c>
-      <x:c r="L7" s="88" t="n">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="M7" s="89" t="str">
-        <x:v>18:50</x:v>
-      </x:c>
-      <x:c r="N7" s="90" t="n">
-        <x:v>46297.25</x:v>
-      </x:c>
-      <x:c r="O7" s="90" t="n">
-        <x:v>46298.958333333336</x:v>
-      </x:c>
-      <x:c r="P7" s="91" t="n">
-        <x:v>0.11</x:v>
-      </x:c>
-      <x:c r="Q7" s="89" t="str">
-        <x:v>M3,1–4,1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="B8" s="17"/>
-      <x:c r="C8" s="3">
-        <x:v>6.0</x:v>
-      </x:c>
-      <x:c r="D8" s="18"/>
-      <x:c r="E8" s="3"/>
-      <x:c r="F8" s="3"/>
-      <x:c r="G8" s="3"/>
-    </x:row>
-    <x:row r="9" ht="15.75" customHeight="1">
-      <x:c r="B9" s="17"/>
-      <x:c r="C9" s="3">
-        <x:v>7.0</x:v>
-      </x:c>
-      <x:c r="D9" s="18"/>
-      <x:c r="E9" s="3"/>
-      <x:c r="F9" s="3"/>
-      <x:c r="G9" s="3"/>
-    </x:row>
-    <x:row r="10" ht="15.75" customHeight="1">
-      <x:c r="B10" s="17"/>
-      <x:c r="C10" s="3">
-        <x:v>8.0</x:v>
-      </x:c>
-      <x:c r="D10" s="18"/>
-      <x:c r="E10" s="3"/>
-      <x:c r="F10" s="3"/>
-      <x:c r="G10" s="3"/>
-    </x:row>
-    <x:row r="11" ht="15.75" customHeight="1">
-      <x:c r="B11" s="17"/>
-      <x:c r="C11" s="3">
-        <x:v>9.0</x:v>
-      </x:c>
-      <x:c r="D11" s="18"/>
-      <x:c r="E11" s="3"/>
-      <x:c r="F11" s="3"/>
-      <x:c r="G11" s="3"/>
-    </x:row>
-    <x:row r="12" ht="15.75" customHeight="1">
-      <x:c r="B12" s="29"/>
-      <x:c r="C12" s="3">
-        <x:v>10.0</x:v>
-      </x:c>
-      <x:c r="D12" s="18"/>
-      <x:c r="E12" s="3"/>
-      <x:c r="F12" s="3"/>
-      <x:c r="G12" s="3"/>
+      <x:c r="I12" t="n">
+        <x:v>-71.8</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Franja costera</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>Referencia aproximada frente a San Antonio</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1">
       <x:c r="D13" s="13"/>
@@ -9526,16 +9507,16 @@
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>108</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E3" s="16" t="s">
-        <x:v>110</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
         <x:v>24</x:v>
@@ -9548,10 +9529,10 @@
         <x:v>-70.35</x:v>
       </x:c>
       <x:c r="J3" s="16" t="s">
-        <x:v>111</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K3" s="16" t="s">
-        <x:v>112</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15.75" customHeight="1">
@@ -9560,13 +9541,13 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>115</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G4" s="3"/>
       <x:c r="H4" s="16">
@@ -9576,10 +9557,10 @@
         <x:v>-71.85</x:v>
       </x:c>
       <x:c r="J4" s="16" t="s">
-        <x:v>111</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K4" s="16" t="s">
-        <x:v>116</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15.75" customHeight="1">
@@ -9588,13 +9569,13 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>117</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
-        <x:v>119</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G5" s="3"/>
       <x:c r="H5" s="16">
@@ -9604,10 +9585,10 @@
         <x:v>-73.1</x:v>
       </x:c>
       <x:c r="J5" s="16" t="s">
-        <x:v>120</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K5" s="16" t="s">
-        <x:v>121</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15.75" customHeight="1">
@@ -9616,13 +9597,13 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>122</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>123</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G6" s="3"/>
       <x:c r="H6" s="16">
@@ -9632,10 +9613,10 @@
         <x:v>-70.65</x:v>
       </x:c>
       <x:c r="J6" s="16" t="s">
-        <x:v>111</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K6" s="16" t="s">
-        <x:v>125</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15.75" customHeight="1">
@@ -9644,13 +9625,13 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F7" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G7" s="3"/>
       <x:c r="H7" s="16">
@@ -9660,10 +9641,10 @@
         <x:v>-73.4</x:v>
       </x:c>
       <x:c r="J7" s="16" t="s">
-        <x:v>120</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K7" s="16" t="s">
-        <x:v>128</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
@@ -9672,15 +9653,27 @@
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="D8" s="24" t="s">
-        <x:v>129</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E8" s="24" t="s">
-        <x:v>130</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F8" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G8" s="3"/>
+      <x:c r="H8" t="n">
+        <x:v>-23</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>-68.8</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Zona interior</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>Referencia aproximada interior de Antofagasta</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
       <x:c r="B9" s="17"/>
@@ -9688,15 +9681,27 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="D9" s="24" t="s">
-        <x:v>129</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E9" s="24" t="s">
-        <x:v>132</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F9" s="24" t="s">
-        <x:v>133</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G9" s="3"/>
+      <x:c r="H9" t="n">
+        <x:v>-20.5</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>-69.4</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Corredor interior</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>Centro aproximado Iquique–Pica–Camiña</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
       <x:c r="B10" s="17"/>
@@ -9704,15 +9709,27 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="D10" s="24" t="s">
-        <x:v>129</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E10" s="24" t="s">
-        <x:v>134</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F10" s="24" t="s">
-        <x:v>131</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G10" s="3"/>
+      <x:c r="H10" t="n">
+        <x:v>-32</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>-71.5</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Macro-zona costera</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>Centro aproximado Coquimbo–Valparaíso</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
       <x:c r="B11" s="17"/>
@@ -9720,15 +9737,27 @@
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="D11" s="24" t="s">
-        <x:v>129</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E11" s="24" t="s">
-        <x:v>135</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F11" s="24" t="s">
-        <x:v>136</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G11" s="3"/>
+      <x:c r="H11" t="n">
+        <x:v>-36.5</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>-73.2</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Franja costera centro-sur</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>Referencia aproximada costa centro-sur de Chile</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
       <x:c r="B12" s="29"/>
@@ -9736,15 +9765,27 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="D12" s="24" t="s">
-        <x:v>129</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E12" s="24" t="s">
-        <x:v>137</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F12" s="24" t="s">
-        <x:v>138</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G12" s="3"/>
+      <x:c r="H12" t="n">
+        <x:v>-21.8</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>-69.8</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Macro-zona norte</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>Centro aproximado Arica–Antofagasta</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -9755,7 +9796,7 @@
     <x:row r="19" ht="15.75" customHeight="1"/>
     <x:row r="20" ht="15.75" customHeight="1">
       <x:c r="H20" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -10795,19 +10836,19 @@
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="D3" s="19" t="s">
-        <x:v>141</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>142</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>143</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20">
@@ -10817,10 +10858,10 @@
         <x:v>-71.5</x:v>
       </x:c>
       <x:c r="J3" s="20" t="s">
-        <x:v>144</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K3" s="20" t="s">
-        <x:v>145</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -10829,13 +10870,13 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="D4" s="19" t="s">
-        <x:v>146</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E4" s="19" t="s">
-        <x:v>147</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F4" s="19" t="s">
-        <x:v>148</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G4" s="19"/>
       <x:c r="H4" s="20">
@@ -10845,10 +10886,10 @@
         <x:v>-71.4</x:v>
       </x:c>
       <x:c r="J4" s="20" t="s">
-        <x:v>144</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K4" s="20" t="s">
-        <x:v>149</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
@@ -10857,13 +10898,13 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="D5" s="19" t="s">
-        <x:v>150</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E5" s="19" t="s">
-        <x:v>151</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F5" s="19" t="s">
-        <x:v>152</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G5" s="19"/>
       <x:c r="H5" s="20">
@@ -10873,10 +10914,10 @@
         <x:v>-72.3</x:v>
       </x:c>
       <x:c r="J5" s="20" t="s">
-        <x:v>144</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K5" s="20" t="s">
-        <x:v>153</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
@@ -10885,13 +10926,13 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="D6" s="19" t="s">
-        <x:v>154</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E6" s="19" t="s">
-        <x:v>155</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="F6" s="19" t="s">
-        <x:v>156</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G6" s="19"/>
       <x:c r="H6" s="20">
@@ -10901,10 +10942,10 @@
         <x:v>-70.2</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>144</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K6" s="20" t="s">
-        <x:v>157</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -10913,13 +10954,13 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="D7" s="19" t="s">
-        <x:v>158</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E7" s="19" t="s">
-        <x:v>159</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F7" s="19" t="s">
-        <x:v>160</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G7" s="19"/>
       <x:c r="H7" s="20">
@@ -10929,10 +10970,10 @@
         <x:v>-72.9</x:v>
       </x:c>
       <x:c r="J7" s="20" t="s">
-        <x:v>144</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K7" s="20" t="s">
-        <x:v>161</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
@@ -10941,15 +10982,27 @@
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="D8" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E8" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F8" s="31" t="s">
-        <x:v>164</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G8" s="3"/>
+      <x:c r="H8" t="n">
+        <x:v>-22.1</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>-68.8</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Zona interior/altiplánica</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>Referencia aproximada Calama–Ollagüe</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15.75" customHeight="1">
       <x:c r="B9" s="17"/>
@@ -10957,15 +11010,27 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="D9" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E9" s="31" t="s">
-        <x:v>165</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F9" s="31" t="s">
-        <x:v>166</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G9" s="3"/>
+      <x:c r="H9" t="n">
+        <x:v>-30.5</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>-71.3</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Zona regional</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>Centro aproximado La Serena–Coquimbo–Illapel</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15.75" customHeight="1">
       <x:c r="B10" s="17"/>
@@ -10973,15 +11038,27 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="D10" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E10" s="31" t="s">
-        <x:v>167</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="F10" s="31" t="s">
-        <x:v>168</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G10" s="3"/>
+      <x:c r="H10" t="n">
+        <x:v>-33.3</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>-72</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Zona offshore costera</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>Referencia frente a San Antonio–Valparaíso</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1">
       <x:c r="B11" s="17"/>
@@ -10989,15 +11066,27 @@
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="D11" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E11" s="31" t="s">
-        <x:v>169</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F11" s="31" t="s">
-        <x:v>170</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G11" s="3"/>
+      <x:c r="H11" t="n">
+        <x:v>-37.4</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>-71.4</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Zona cordillerana</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>Referencia aproximada Antuco–Alto Biobío</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15.75" customHeight="1">
       <x:c r="B12" s="29"/>
@@ -11005,15 +11094,27 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="D12" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E12" s="31" t="s">
-        <x:v>171</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="F12" s="31" t="s">
-        <x:v>172</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G12" s="3"/>
+      <x:c r="H12" t="n">
+        <x:v>-20.1</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>-69.3</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Zona interior</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>Referencia aproximada Camiña–Huara, al E/SE de Iquique</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15.75" customHeight="1"/>
     <x:row r="14" ht="15.75" customHeight="1"/>
@@ -12060,19 +12161,19 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>173</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="D3" s="19" t="s">
-        <x:v>174</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>175</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>176</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20">
@@ -12082,10 +12183,10 @@
         <x:v>-68.2</x:v>
       </x:c>
       <x:c r="J3" s="20" t="s">
-        <x:v>177</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K3" s="20" t="s">
-        <x:v>178</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
@@ -12094,13 +12195,13 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="D4" s="19" t="s">
-        <x:v>179</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E4" s="19" t="s">
-        <x:v>180</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F4" s="19" t="s">
-        <x:v>181</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G4" s="19"/>
       <x:c r="H4" s="20">
@@ -12110,10 +12211,10 @@
         <x:v>-71.4</x:v>
       </x:c>
       <x:c r="J4" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K4" s="20" t="s">
-        <x:v>183</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
@@ -12122,13 +12223,13 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="D5" s="19" t="s">
-        <x:v>184</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E5" s="19" t="s">
-        <x:v>185</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F5" s="19" t="s">
-        <x:v>186</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G5" s="19"/>
       <x:c r="H5" s="20">
@@ -12138,10 +12239,10 @@
         <x:v>-71.6</x:v>
       </x:c>
       <x:c r="J5" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K5" s="20" t="s">
-        <x:v>187</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
@@ -12150,13 +12251,13 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="D6" s="19" t="s">
-        <x:v>188</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E6" s="19" t="s">
-        <x:v>189</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F6" s="19" t="s">
-        <x:v>190</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G6" s="19"/>
       <x:c r="H6" s="20">
@@ -12166,10 +12267,10 @@
         <x:v>-69.33</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>177</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K6" s="20" t="s">
-        <x:v>191</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -12178,13 +12279,13 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="D7" s="19" t="s">
-        <x:v>192</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E7" s="19" t="s">
-        <x:v>193</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F7" s="19" t="s">
-        <x:v>194</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G7" s="19"/>
       <x:c r="H7" s="20">
@@ -12194,10 +12295,10 @@
         <x:v>-72.0</x:v>
       </x:c>
       <x:c r="J7" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K7" s="20" t="s">
-        <x:v>195</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
@@ -13295,19 +13396,19 @@
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>196</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="D3" s="19" t="s">
-        <x:v>197</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>198</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>199</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20">
@@ -13317,10 +13418,10 @@
         <x:v>-71.613</x:v>
       </x:c>
       <x:c r="J3" s="20" t="s">
-        <x:v>200</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K3" s="20" t="s">
-        <x:v>201</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
@@ -13329,13 +13430,13 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="D4" s="19" t="s">
-        <x:v>202</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E4" s="19" t="s">
-        <x:v>203</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F4" s="19" t="s">
-        <x:v>204</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G4" s="19"/>
       <x:c r="H4" s="20">
@@ -13345,10 +13446,10 @@
         <x:v>-73.05</x:v>
       </x:c>
       <x:c r="J4" s="20" t="s">
-        <x:v>200</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K4" s="20" t="s">
-        <x:v>205</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
@@ -13357,13 +13458,13 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="D5" s="19" t="s">
-        <x:v>206</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E5" s="19" t="s">
-        <x:v>207</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="F5" s="19" t="s">
-        <x:v>208</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G5" s="19"/>
       <x:c r="H5" s="20">
@@ -13373,10 +13474,10 @@
         <x:v>-70.135</x:v>
       </x:c>
       <x:c r="J5" s="20" t="s">
-        <x:v>200</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K5" s="20" t="s">
-        <x:v>209</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
@@ -13385,13 +13486,13 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="D6" s="19" t="s">
-        <x:v>210</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E6" s="19" t="s">
-        <x:v>211</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="F6" s="19" t="s">
-        <x:v>212</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G6" s="19"/>
       <x:c r="H6" s="20">
@@ -13401,10 +13502,10 @@
         <x:v>-72.942</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>213</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="K6" s="20" t="s">
-        <x:v>214</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -13413,13 +13514,13 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="D7" s="19" t="s">
-        <x:v>215</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E7" s="19" t="s">
-        <x:v>216</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="F7" s="19" t="s">
-        <x:v>217</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G7" s="19"/>
       <x:c r="H7" s="20">
@@ -13429,10 +13530,10 @@
         <x:v>-70.33</x:v>
       </x:c>
       <x:c r="J7" s="20" t="s">
-        <x:v>218</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="K7" s="20" t="s">
-        <x:v>219</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
@@ -14530,19 +14631,19 @@
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="B3" s="7" t="s">
-        <x:v>220</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C3" s="3">
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="D3" s="19" t="s">
-        <x:v>221</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>222</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>223</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20">
@@ -14552,10 +14653,10 @@
         <x:v>-69.3</x:v>
       </x:c>
       <x:c r="J3" s="20" t="s">
-        <x:v>224</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K3" s="20" t="s">
-        <x:v>225</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -14564,13 +14665,13 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="D4" s="19" t="s">
-        <x:v>226</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E4" s="19" t="s">
-        <x:v>227</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="F4" s="19" t="s">
-        <x:v>228</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G4" s="19"/>
       <x:c r="H4" s="20">
@@ -14580,10 +14681,10 @@
         <x:v>-68.1</x:v>
       </x:c>
       <x:c r="J4" s="20" t="s">
-        <x:v>229</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="K4" s="20" t="s">
-        <x:v>230</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
@@ -14592,13 +14693,13 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="D5" s="19" t="s">
-        <x:v>231</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E5" s="19" t="s">
-        <x:v>232</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="F5" s="19" t="s">
-        <x:v>233</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G5" s="19"/>
       <x:c r="H5" s="20">
@@ -14608,10 +14709,10 @@
         <x:v>-71.8</x:v>
       </x:c>
       <x:c r="J5" s="20" t="s">
-        <x:v>234</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="K5" s="20" t="s">
-        <x:v>235</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -14620,13 +14721,13 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="D6" s="19" t="s">
-        <x:v>236</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E6" s="19" t="s">
-        <x:v>237</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F6" s="19" t="s">
-        <x:v>238</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G6" s="19"/>
       <x:c r="H6" s="20">
@@ -14636,10 +14737,10 @@
         <x:v>-70.9</x:v>
       </x:c>
       <x:c r="J6" s="20" t="s">
-        <x:v>239</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K6" s="20" t="s">
-        <x:v>240</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -14648,13 +14749,13 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="D7" s="32" t="s">
-        <x:v>241</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E7" s="19" t="s">
-        <x:v>242</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F7" s="19" t="s">
-        <x:v>243</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G7" s="19"/>
       <x:c r="H7" s="20">
@@ -14664,10 +14765,10 @@
         <x:v>-73.6</x:v>
       </x:c>
       <x:c r="J7" s="20" t="s">
-        <x:v>244</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K7" s="20" t="s">
-        <x:v>245</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
